--- a/posts/inflation suisse/inflation_income_decomposition.xlsx
+++ b/posts/inflation suisse/inflation_income_decomposition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\celalguney\posts\inflation suisse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A35480A-2D8E-4091-81F8-AEB8FD27FD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8C5CA1-E420-42CA-8B4A-4C596758C130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
   </bookViews>
   <sheets>
     <sheet name="data source" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="163">
   <si>
     <t>deflator</t>
   </si>
@@ -524,6 +524,12 @@
   </si>
   <si>
     <t>2026-1</t>
+  </si>
+  <si>
+    <t>inflation 2020-2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profit </t>
   </si>
 </sst>
 </file>
@@ -574,13 +580,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,14 +935,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DA2C05D-65D1-46AA-8FA9-9F5E22D2C41F}">
-  <dimension ref="A1:R146"/>
+  <dimension ref="A1:W146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="8" max="8" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.453125" customWidth="1"/>
+    <col min="20" max="20" width="17.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
         <v>19</v>
       </c>
@@ -972,7 +980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -992,19 +1000,19 @@
         <v>90810.987888469404</v>
       </c>
       <c r="G2">
-        <f>F2/(E2)</f>
+        <f t="shared" ref="G2:G33" si="0">F2/(E2)</f>
         <v>1126.4708856106563</v>
       </c>
       <c r="H2">
-        <f>D2/G2</f>
+        <f t="shared" ref="H2:H33" si="1">D2/G2</f>
         <v>32.481288740384102</v>
       </c>
       <c r="I2">
-        <f>C2/G2</f>
+        <f t="shared" ref="I2:I33" si="2">C2/G2</f>
         <v>48.134188364681933</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1990</v>
       </c>
@@ -1024,24 +1032,23 @@
         <v>93568.517690094304</v>
       </c>
       <c r="G3">
-        <f>F3/(E3)</f>
+        <f t="shared" si="0"/>
         <v>1148.3705904442388</v>
       </c>
       <c r="H3">
-        <f>D3/G3</f>
+        <f t="shared" si="1"/>
         <v>38.216431905247049</v>
       </c>
       <c r="I3">
-        <f>C3/G3</f>
+        <f t="shared" si="2"/>
         <v>43.262942844238651</v>
       </c>
-      <c r="J3" s="5">
-        <f>(E3-E2)/E2</f>
+      <c r="J3">
+        <f t="shared" ref="J3:J34" si="3">(E3-E2)/E2</f>
         <v>1.0716275279170989E-2</v>
       </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1990</v>
       </c>
@@ -1061,24 +1068,23 @@
         <v>93527.045927184299</v>
       </c>
       <c r="G4">
-        <f>F4/(E4)</f>
+        <f t="shared" si="0"/>
         <v>1138.5543162782515</v>
       </c>
       <c r="H4">
-        <f>D4/G4</f>
+        <f t="shared" si="1"/>
         <v>39.093211996251597</v>
       </c>
       <c r="I4">
-        <f>C4/G4</f>
+        <f t="shared" si="2"/>
         <v>43.052228576938489</v>
       </c>
-      <c r="J4" s="5">
-        <f>(E4-E3)/E3</f>
+      <c r="J4">
+        <f t="shared" si="3"/>
         <v>8.1746555585676499E-3</v>
       </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1990</v>
       </c>
@@ -1098,22 +1104,21 @@
         <v>96855.485112819006</v>
       </c>
       <c r="G5">
-        <f>F5/(E5)</f>
+        <f t="shared" si="0"/>
         <v>1167.233379937235</v>
       </c>
       <c r="H5">
-        <f>D5/G5</f>
+        <f t="shared" si="1"/>
         <v>39.448346357807452</v>
       </c>
       <c r="I5">
-        <f>C5/G5</f>
+        <f t="shared" si="2"/>
         <v>43.530333636785542</v>
       </c>
-      <c r="J5" s="5">
-        <f>(E5-E4)/E4</f>
+      <c r="J5">
+        <f t="shared" si="3"/>
         <v>1.0143465243946097E-2</v>
       </c>
-      <c r="K5" s="5"/>
       <c r="N5" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1131,17 @@
       <c r="R5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T5" t="s">
+        <v>161</v>
+      </c>
+      <c r="U5" t="s">
+        <v>162</v>
+      </c>
+      <c r="V5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1991</v>
       </c>
@@ -1147,19 +1161,19 @@
         <v>95642.069279736301</v>
       </c>
       <c r="G6">
-        <f>F6/(E6)</f>
+        <f t="shared" si="0"/>
         <v>1124.1473734654514</v>
       </c>
       <c r="H6">
-        <f>D6/G6</f>
+        <f t="shared" si="1"/>
         <v>33.844605144542577</v>
       </c>
       <c r="I6">
-        <f>C6/G6</f>
+        <f t="shared" si="2"/>
         <v>51.235048588843675</v>
       </c>
-      <c r="J6" s="5">
-        <f>(E6-E5)/E5</f>
+      <c r="J6">
+        <f t="shared" si="3"/>
         <v>2.5319440354199446E-2</v>
       </c>
       <c r="K6" s="4">
@@ -1194,8 +1208,24 @@
         <f>E6/E2-1</f>
         <v>5.5376173268838036E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T6">
+        <f>E133/E122 - 1</f>
+        <v>5.4201523779288108E-2</v>
+      </c>
+      <c r="U6">
+        <f>(H133-H122)/(E133-E122)*T6</f>
+        <v>0.12656103516813291</v>
+      </c>
+      <c r="V6">
+        <f>(I133-I122)/(E133-E122)*T6</f>
+        <v>-7.2359511388841682E-2</v>
+      </c>
+      <c r="W6">
+        <f>V6+U6</f>
+        <v>5.420152377929123E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1991</v>
       </c>
@@ -1215,31 +1245,31 @@
         <v>97602.376101816</v>
       </c>
       <c r="G7">
-        <f>F7/(E7)</f>
+        <f t="shared" si="0"/>
         <v>1133.4549366019937</v>
       </c>
       <c r="H7">
-        <f>D7/G7</f>
+        <f t="shared" si="1"/>
         <v>38.589778627072832</v>
       </c>
       <c r="I7">
-        <f>C7/G7</f>
+        <f t="shared" si="2"/>
         <v>47.520725593253687</v>
       </c>
-      <c r="J7" s="5">
-        <f>(E7-E6)/E6</f>
+      <c r="J7">
+        <f t="shared" si="3"/>
         <v>1.2116298570874309E-2</v>
       </c>
       <c r="K7" s="4">
-        <f>(E7-E3)/E3</f>
+        <f t="shared" ref="K6:K37" si="4">(E7-E3)/E3</f>
         <v>5.6838058528058788E-2</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L70" si="0">(H7-H3)/(E7-E3)</f>
+        <f t="shared" ref="L7:L70" si="5">(H7-H3)/(E7-E3)</f>
         <v>8.0616774844343084E-2</v>
       </c>
       <c r="M7">
-        <f t="shared" ref="M7:M70" si="1">(I7-I3)/(E7-E3)</f>
+        <f t="shared" ref="M7:M70" si="6">(I7-I3)/(E7-E3)</f>
         <v>0.91938322515563853</v>
       </c>
       <c r="N7">
@@ -1247,23 +1277,23 @@
         <v>0.99999999999998157</v>
       </c>
       <c r="O7" t="str">
-        <f t="shared" ref="O7:O70" si="2">"Q"&amp;A7&amp;"-"&amp;B7</f>
+        <f t="shared" ref="O7:O70" si="7">"Q"&amp;A7&amp;"-"&amp;B7</f>
         <v>Q1991-2</v>
       </c>
       <c r="P7">
-        <f t="shared" ref="P7:P70" si="3">L7*K7</f>
+        <f t="shared" ref="P7:P70" si="8">L7*K7</f>
         <v>4.5821009669461095E-3</v>
       </c>
       <c r="Q7">
-        <f t="shared" ref="Q7:Q70" si="4">M7*K7</f>
+        <f t="shared" ref="Q7:Q70" si="9">M7*K7</f>
         <v>5.2255957561111635E-2</v>
       </c>
       <c r="R7">
-        <f t="shared" ref="R7:R70" si="5">E7/E3-1</f>
+        <f t="shared" ref="R7:R70" si="10">E7/E3-1</f>
         <v>5.6838058528058788E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1991</v>
       </c>
@@ -1283,55 +1313,55 @@
         <v>97494.693818346597</v>
       </c>
       <c r="G8">
-        <f>F8/(E8)</f>
+        <f t="shared" si="0"/>
         <v>1123.4578396347513</v>
       </c>
       <c r="H8">
-        <f>D8/G8</f>
+        <f t="shared" si="1"/>
         <v>39.89854514199272</v>
       </c>
       <c r="I8">
-        <f>C8/G8</f>
+        <f t="shared" si="2"/>
         <v>46.882364989929329</v>
       </c>
-      <c r="J8" s="5">
-        <f>(E8-E7)/E7</f>
+      <c r="J8">
+        <f t="shared" si="3"/>
         <v>7.7854138431248934E-3</v>
       </c>
       <c r="K8" s="4">
-        <f>(E8-E4)/E4</f>
+        <f t="shared" si="4"/>
         <v>5.6430028573547841E-2</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.17373280862650112</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.8262671913735341</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N8:N70" si="6">M8+L8</f>
+        <f t="shared" ref="N8:N70" si="11">M8+L8</f>
         <v>1.0000000000000353</v>
       </c>
       <c r="O8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1991-3</v>
       </c>
       <c r="P8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>9.8037473549561771E-3</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4.6626281218593649E-2</v>
       </c>
       <c r="R8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.643002857354773E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1991</v>
       </c>
@@ -1351,55 +1381,55 @@
         <v>100676.388351384</v>
       </c>
       <c r="G9">
-        <f>F9/(E9)</f>
+        <f t="shared" si="0"/>
         <v>1157.6188615381723</v>
       </c>
       <c r="H9">
-        <f>D9/G9</f>
+        <f t="shared" si="1"/>
         <v>39.794401252493401</v>
       </c>
       <c r="I9">
-        <f>C9/G9</f>
+        <f t="shared" si="2"/>
         <v>47.174109451981195</v>
       </c>
-      <c r="J9" s="5">
-        <f>(E9-E8)/E8</f>
+      <c r="J9">
+        <f t="shared" si="3"/>
         <v>2.1617723560079377E-3</v>
       </c>
       <c r="K9" s="4">
-        <f>(E9-E5)/E5</f>
+        <f t="shared" si="4"/>
         <v>4.8082600375679463E-2</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8.6734230058657144E-2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.91326576994139275</v>
       </c>
       <c r="N9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.00000000000005</v>
       </c>
       <c r="O9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1991-4</v>
       </c>
       <c r="P9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>4.1704073228026571E-3</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4.3912193052879203E-2</v>
       </c>
       <c r="R9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.8082600375679352E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1992</v>
       </c>
@@ -1419,55 +1449,55 @@
         <v>98942.184140785204</v>
       </c>
       <c r="G10">
-        <f>F10/(E10)</f>
+        <f t="shared" si="0"/>
         <v>1125.1488330763714</v>
       </c>
       <c r="H10">
-        <f>D10/G10</f>
+        <f t="shared" si="1"/>
         <v>35.46048238620719</v>
       </c>
       <c r="I10">
-        <f>C10/G10</f>
+        <f t="shared" si="2"/>
         <v>52.476492022999061</v>
       </c>
-      <c r="J10" s="5">
-        <f>(E10-E9)/E9</f>
+      <c r="J10">
+        <f t="shared" si="3"/>
         <v>1.1135797277509053E-2</v>
       </c>
       <c r="K10" s="4">
-        <f>(E10-E6)/E6</f>
+        <f t="shared" si="4"/>
         <v>3.3584065642462274E-2</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.56552183846178972</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.43447816153820784</v>
       </c>
       <c r="N10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999999756</v>
       </c>
       <c r="O10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1992-1</v>
       </c>
       <c r="P10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.8992522545146693E-2</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.45915430973155E-2</v>
       </c>
       <c r="R10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.3584065642462191E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1992</v>
       </c>
@@ -1487,55 +1517,55 @@
         <v>100200.68982937701</v>
       </c>
       <c r="G11">
-        <f>F11/(E11)</f>
+        <f t="shared" si="0"/>
         <v>1138.4278085330018</v>
       </c>
       <c r="H11">
-        <f>D11/G11</f>
+        <f t="shared" si="1"/>
         <v>39.12417696466315</v>
       </c>
       <c r="I11">
-        <f>C11/G11</f>
+        <f t="shared" si="2"/>
         <v>48.892550207960824</v>
       </c>
-      <c r="J11" s="5">
-        <f>(E11-E10)/E10</f>
+      <c r="J11">
+        <f t="shared" si="3"/>
         <v>9.0693094631823224E-4</v>
       </c>
       <c r="K11" s="4">
-        <f>(E11-E7)/E7</f>
+        <f t="shared" si="4"/>
         <v>2.2136938687754557E-2</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.28034408931356508</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.71965591068667345</v>
       </c>
       <c r="N11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000002385</v>
       </c>
       <c r="O11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1992-2</v>
       </c>
       <c r="P11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>6.2059599166087772E-3</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.5930978771151058E-2</v>
       </c>
       <c r="R11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.213693868775457E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1992</v>
       </c>
@@ -1555,55 +1585,55 @@
         <v>98954.020189139803</v>
       </c>
       <c r="G12">
-        <f>F12/(E12)</f>
+        <f t="shared" si="0"/>
         <v>1123.846712323689</v>
       </c>
       <c r="H12">
-        <f>D12/G12</f>
+        <f t="shared" si="1"/>
         <v>39.269915545471044</v>
       </c>
       <c r="I12">
-        <f>C12/G12</f>
+        <f t="shared" si="2"/>
         <v>48.779476870813525</v>
       </c>
-      <c r="J12" s="5">
-        <f>(E12-E11)/E11</f>
+      <c r="J12">
+        <f t="shared" si="3"/>
         <v>3.7112540661657898E-4</v>
       </c>
       <c r="K12" s="4">
-        <f>(E12-E8)/E8</f>
+        <f t="shared" si="4"/>
         <v>1.4617065924225646E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.49557617340911808</v>
       </c>
       <c r="M12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.4955761734090509</v>
       </c>
       <c r="N12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999993283</v>
       </c>
       <c r="O12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1992-3</v>
       </c>
       <c r="P12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-7.2438695971965596E-3</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.1860935521421224E-2</v>
       </c>
       <c r="R12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.4617065924225736E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1992</v>
       </c>
@@ -1623,55 +1653,55 @@
         <v>101459.970091453</v>
       </c>
       <c r="G13">
-        <f>F13/(E13)</f>
+        <f t="shared" si="0"/>
         <v>1149.2707571343385</v>
       </c>
       <c r="H13">
-        <f>D13/G13</f>
+        <f t="shared" si="1"/>
         <v>39.364813842043901</v>
       </c>
       <c r="I13">
-        <f>C13/G13</f>
+        <f t="shared" si="2"/>
         <v>48.917228889505218</v>
       </c>
-      <c r="J13" s="5">
-        <f>(E13-E12)/E12</f>
+      <c r="J13">
+        <f t="shared" si="3"/>
         <v>2.6422705356575179E-3</v>
       </c>
       <c r="K13" s="4">
-        <f>(E13-E9)/E9</f>
+        <f t="shared" si="4"/>
         <v>1.5103535940011481E-2</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.32704753412548465</v>
       </c>
       <c r="M13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.3270475341256522</v>
       </c>
       <c r="N13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001676</v>
       </c>
       <c r="O13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1992-4</v>
       </c>
       <c r="P13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-4.939574185756389E-3</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.00431101257704E-2</v>
       </c>
       <c r="R13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.510353594001157E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1993</v>
       </c>
@@ -1691,55 +1721,55 @@
         <v>98779.554404440103</v>
       </c>
       <c r="G14">
-        <f>F14/(E14)</f>
+        <f t="shared" si="0"/>
         <v>1103.5936206784334</v>
       </c>
       <c r="H14">
-        <f>D14/G14</f>
+        <f t="shared" si="1"/>
         <v>35.378173697378543</v>
       </c>
       <c r="I14">
-        <f>C14/G14</f>
+        <f t="shared" si="2"/>
         <v>54.129007708504673</v>
       </c>
-      <c r="J14" s="5">
-        <f>(E14-E13)/E13</f>
+      <c r="J14">
+        <f t="shared" si="3"/>
         <v>1.3877552403947524E-2</v>
       </c>
       <c r="K14" s="4">
-        <f>(E14-E10)/E10</f>
+        <f t="shared" si="4"/>
         <v>1.7856049826892987E-2</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-5.2419005266716508E-2</v>
       </c>
       <c r="M14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.052419005266694</v>
       </c>
       <c r="N14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999997746</v>
       </c>
       <c r="O14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1993-1</v>
       </c>
       <c r="P14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-9.3599636991865585E-4</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.8792046196811241E-2</v>
       </c>
       <c r="R14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.7856049826892928E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1993</v>
       </c>
@@ -1759,55 +1789,55 @@
         <v>101557.582148256</v>
       </c>
       <c r="G15">
-        <f>F15/(E15)</f>
+        <f t="shared" si="0"/>
         <v>1128.5398230312348</v>
       </c>
       <c r="H15">
-        <f>D15/G15</f>
+        <f t="shared" si="1"/>
         <v>40.027006694745985</v>
       </c>
       <c r="I15">
-        <f>C15/G15</f>
+        <f t="shared" si="2"/>
         <v>49.963244491494656</v>
       </c>
-      <c r="J15" s="5">
-        <f>(E15-E14)/E14</f>
+      <c r="J15">
+        <f t="shared" si="3"/>
         <v>5.3969946631036115E-3</v>
       </c>
       <c r="K15" s="4">
-        <f>(E15-E11)/E11</f>
+        <f t="shared" si="4"/>
         <v>2.2422147210110467E-2</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.45747086118719293</v>
       </c>
       <c r="M15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.54252913881279263</v>
       </c>
       <c r="N15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999998557</v>
       </c>
       <c r="O15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1993-2</v>
       </c>
       <c r="P15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.0257478993875252E-2</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.2164668216234893E-2</v>
       </c>
       <c r="R15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.2422147210110488E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1993</v>
       </c>
@@ -1827,51 +1857,51 @@
         <v>102202.90030377499</v>
       </c>
       <c r="G16">
-        <f>F16/(E16)</f>
+        <f t="shared" si="0"/>
         <v>1130.7279655946691</v>
       </c>
       <c r="H16">
-        <f>D16/G16</f>
+        <f t="shared" si="1"/>
         <v>41.566986422221596</v>
       </c>
       <c r="I16">
-        <f>C16/G16</f>
+        <f t="shared" si="2"/>
         <v>48.819829340334529</v>
       </c>
-      <c r="J16" s="5">
-        <f>(E16-E15)/E15</f>
+      <c r="J16">
+        <f t="shared" si="3"/>
         <v>4.4067504100514521E-3</v>
       </c>
       <c r="K16" s="4">
-        <f>(E16-E12)/E12</f>
+        <f t="shared" si="4"/>
         <v>2.6546728854417292E-2</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.98273634530727516</v>
       </c>
       <c r="M16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.7263654692837263E-2</v>
       </c>
       <c r="N16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001124</v>
       </c>
       <c r="O16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1993-3</v>
       </c>
       <c r="P16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.6088435294253236E-2</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4.5829356016703946E-4</v>
       </c>
       <c r="R16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.6546728854417223E-2</v>
       </c>
     </row>
@@ -1895,51 +1925,51 @@
         <v>105779.569349952</v>
       </c>
       <c r="G17">
-        <f>F17/(E17)</f>
+        <f t="shared" si="0"/>
         <v>1168.1172136487455</v>
       </c>
       <c r="H17">
-        <f>D17/G17</f>
+        <f t="shared" si="1"/>
         <v>41.630585211819238</v>
       </c>
       <c r="I17">
-        <f>C17/G17</f>
+        <f t="shared" si="2"/>
         <v>48.925026942493488</v>
       </c>
-      <c r="J17" s="5">
-        <f>(E17-E16)/E16</f>
+      <c r="J17">
+        <f t="shared" si="3"/>
         <v>1.867489083806483E-3</v>
       </c>
       <c r="K17" s="4">
-        <f>(E17-E13)/E13</f>
+        <f t="shared" si="4"/>
         <v>2.5753475479462492E-2</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.99657012761062591</v>
       </c>
       <c r="M17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.4298723892896904E-3</v>
       </c>
       <c r="N17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999991562</v>
       </c>
       <c r="O17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1993-4</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.5665144344985062E-2</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8.8331134475257473E-5</v>
       </c>
       <c r="R17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.5753475479462384E-2</v>
       </c>
     </row>
@@ -1963,51 +1993,51 @@
         <v>103613.996138203</v>
       </c>
       <c r="G18">
-        <f>F18/(E18)</f>
+        <f t="shared" si="0"/>
         <v>1133.3097995103481</v>
       </c>
       <c r="H18">
-        <f>D18/G18</f>
+        <f t="shared" si="1"/>
         <v>38.461109114108112</v>
       </c>
       <c r="I18">
-        <f>C18/G18</f>
+        <f t="shared" si="2"/>
         <v>52.964903599247329</v>
       </c>
-      <c r="J18" s="5">
-        <f>(E18-E17)/E17</f>
+      <c r="J18">
+        <f t="shared" si="3"/>
         <v>9.6117793070559787E-3</v>
       </c>
       <c r="K18" s="4">
-        <f>(E18-E14)/E14</f>
+        <f t="shared" si="4"/>
         <v>2.1437735803237802E-2</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.6066735021076723</v>
       </c>
       <c r="M18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.60667350210745374</v>
       </c>
       <c r="N18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000002185</v>
       </c>
       <c r="O18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1994-1</v>
       </c>
       <c r="P18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>3.4443442060247111E-2</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.3005706257004625E-2</v>
       </c>
       <c r="R18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.1437735803237823E-2</v>
       </c>
     </row>
@@ -2031,51 +2061,51 @@
         <v>103532.204743637</v>
       </c>
       <c r="G19">
-        <f>F19/(E19)</f>
+        <f t="shared" si="0"/>
         <v>1133.4344041409092</v>
       </c>
       <c r="H19">
-        <f>D19/G19</f>
+        <f t="shared" si="1"/>
         <v>41.108957764289777</v>
       </c>
       <c r="I19">
-        <f>C19/G19</f>
+        <f t="shared" si="2"/>
         <v>50.234841546363498</v>
       </c>
-      <c r="J19" s="5">
-        <f>(E19-E18)/E18</f>
+      <c r="J19">
+        <f t="shared" si="3"/>
         <v>-8.9923425797503896E-4</v>
       </c>
       <c r="K19" s="4">
-        <f>(E19-E15)/E15</f>
+        <f t="shared" si="4"/>
         <v>1.5041052853732409E-2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.79934436761388861</v>
       </c>
       <c r="M19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.20065563238591722</v>
       </c>
       <c r="N19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999980582</v>
       </c>
       <c r="O19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1994-2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.2022980881613807E-2</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.0180719721156811E-3</v>
       </c>
       <c r="R19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.5041052853732362E-2</v>
       </c>
     </row>
@@ -2099,51 +2129,51 @@
         <v>104057.660913859</v>
       </c>
       <c r="G20">
-        <f>F20/(E20)</f>
+        <f t="shared" si="0"/>
         <v>1142.0506818658532</v>
       </c>
       <c r="H20">
-        <f>D20/G20</f>
+        <f t="shared" si="1"/>
         <v>42.38472560020044</v>
       </c>
       <c r="I20">
-        <f>C20/G20</f>
+        <f t="shared" si="2"/>
         <v>48.730023128684735</v>
       </c>
-      <c r="J20" s="5">
-        <f>(E20-E19)/E19</f>
+      <c r="J20">
+        <f t="shared" si="3"/>
         <v>-2.5075657406060867E-3</v>
       </c>
       <c r="K20" s="4">
-        <f>(E20-E16)/E16</f>
+        <f t="shared" si="4"/>
         <v>8.053530375949627E-3</v>
       </c>
       <c r="L20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.1233715407925828</v>
       </c>
       <c r="M20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.12337154079266083</v>
       </c>
       <c r="N20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999992206</v>
       </c>
       <c r="O20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1994-3</v>
       </c>
       <c r="P20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>9.0471068272504011E-3</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-9.9357645130140242E-4</v>
       </c>
       <c r="R20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.0535303759496912E-3</v>
       </c>
     </row>
@@ -2167,51 +2197,51 @@
         <v>107197.905315187</v>
       </c>
       <c r="G21">
-        <f>F21/(E21)</f>
+        <f t="shared" si="0"/>
         <v>1179.7161872340841</v>
       </c>
       <c r="H21">
-        <f>D21/G21</f>
+        <f t="shared" si="1"/>
         <v>42.372005369694229</v>
       </c>
       <c r="I21">
-        <f>C21/G21</f>
+        <f t="shared" si="2"/>
         <v>48.495532496781337</v>
       </c>
-      <c r="J21" s="5">
-        <f>(E21-E20)/E20</f>
+      <c r="J21">
+        <f t="shared" si="3"/>
         <v>-2.7131816293022551E-3</v>
       </c>
       <c r="K21" s="4">
-        <f>(E21-E17)/E17</f>
+        <f t="shared" si="4"/>
         <v>3.4445762636032174E-3</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.3769126076019682</v>
       </c>
       <c r="M21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.3769126076018543</v>
       </c>
       <c r="N21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001139</v>
       </c>
       <c r="O21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1994-4</v>
       </c>
       <c r="P21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>8.1874567488049686E-3</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.7428804852013579E-3</v>
       </c>
       <c r="R21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.4445762636032828E-3</v>
       </c>
     </row>
@@ -2235,51 +2265,51 @@
         <v>103647.486476338</v>
       </c>
       <c r="G22">
-        <f>F22/(E22)</f>
+        <f t="shared" si="0"/>
         <v>1130.9551314721459</v>
       </c>
       <c r="H22">
-        <f>D22/G22</f>
+        <f t="shared" si="1"/>
         <v>37.708222179652971</v>
       </c>
       <c r="I22">
-        <f>C22/G22</f>
+        <f t="shared" si="2"/>
         <v>53.937753502354383</v>
       </c>
-      <c r="J22" s="5">
-        <f>(E22-E21)/E21</f>
+      <c r="J22">
+        <f t="shared" si="3"/>
         <v>8.5667316822886745E-3</v>
       </c>
       <c r="K22" s="4">
-        <f>(E22-E18)/E18</f>
+        <f t="shared" si="4"/>
         <v>2.4059123013724579E-3</v>
       </c>
       <c r="L22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-3.4227894770986422</v>
       </c>
       <c r="M22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4227894770959937</v>
       </c>
       <c r="N22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999735145</v>
       </c>
       <c r="O22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1995-1</v>
       </c>
       <c r="P22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-8.2349313079598252E-3</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.0640843609325911E-2</v>
       </c>
       <c r="R22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.4059123013724371E-3</v>
       </c>
     </row>
@@ -2303,51 +2333,51 @@
         <v>105210.540632602</v>
       </c>
       <c r="G23">
-        <f>F23/(E23)</f>
+        <f t="shared" si="0"/>
         <v>1147.0651432029799</v>
       </c>
       <c r="H23">
-        <f>D23/G23</f>
+        <f t="shared" si="1"/>
         <v>41.861628593643751</v>
       </c>
       <c r="I23">
-        <f>C23/G23</f>
+        <f t="shared" si="2"/>
         <v>49.859875852755422</v>
       </c>
-      <c r="J23" s="5">
-        <f>(E23-E22)/E22</f>
+      <c r="J23">
+        <f t="shared" si="3"/>
         <v>8.241361808834219E-4</v>
       </c>
       <c r="K23" s="4">
-        <f>(E23-E19)/E19</f>
+        <f t="shared" si="4"/>
         <v>4.1349838587484726E-3</v>
       </c>
       <c r="L23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.9927471408795259</v>
       </c>
       <c r="M23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.99274714088061711</v>
       </c>
       <c r="N23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999890876</v>
       </c>
       <c r="O23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1995-2</v>
       </c>
       <c r="P23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>8.2399772621040077E-3</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.104993403360048E-3</v>
       </c>
       <c r="R23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.1349838587485532E-3</v>
       </c>
     </row>
@@ -2371,51 +2401,51 @@
         <v>105925.53384225701</v>
       </c>
       <c r="G24">
-        <f>F24/(E24)</f>
+        <f t="shared" si="0"/>
         <v>1149.128071263638</v>
       </c>
       <c r="H24">
-        <f>D24/G24</f>
+        <f t="shared" si="1"/>
         <v>43.110835655288902</v>
       </c>
       <c r="I24">
-        <f>C24/G24</f>
+        <f t="shared" si="2"/>
         <v>49.068214261902455</v>
       </c>
-      <c r="J24" s="5">
-        <f>(E24-E23)/E23</f>
+      <c r="J24">
+        <f t="shared" si="3"/>
         <v>4.9884209112540248E-3</v>
       </c>
       <c r="K24" s="4">
-        <f>(E24-E20)/E20</f>
+        <f t="shared" si="4"/>
         <v>1.1680888145490747E-2</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.6822411391307085</v>
       </c>
       <c r="M24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.31775886086889765</v>
       </c>
       <c r="N24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999960609</v>
       </c>
       <c r="O24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1995-3</v>
       </c>
       <c r="P24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>7.969182434437996E-3</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.7117057110481501E-3</v>
       </c>
       <c r="R24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1680888145490842E-2</v>
       </c>
     </row>
@@ -2439,51 +2469,51 @@
         <v>108731.79454673801</v>
       </c>
       <c r="G25">
-        <f>F25/(E25)</f>
+        <f t="shared" si="0"/>
         <v>1183.4273368482388</v>
       </c>
       <c r="H25">
-        <f>D25/G25</f>
+        <f t="shared" si="1"/>
         <v>40.60075332919174</v>
       </c>
       <c r="I25">
-        <f>C25/G25</f>
+        <f t="shared" si="2"/>
         <v>51.277971423201883</v>
       </c>
-      <c r="J25" s="5">
-        <f>(E25-E24)/E24</f>
+      <c r="J25">
+        <f t="shared" si="3"/>
         <v>-3.258063139806644E-3</v>
       </c>
       <c r="K25" s="4">
-        <f>(E25-E21)/E21</f>
+        <f t="shared" si="4"/>
         <v>1.1128142234959485E-2</v>
       </c>
       <c r="L25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-1.7516564595210657</v>
       </c>
       <c r="M25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.7516564595204263</v>
       </c>
       <c r="N25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999936051</v>
       </c>
       <c r="O25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1995-4</v>
       </c>
       <c r="P25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-1.9492682228335972E-2</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.062082446328834E-2</v>
       </c>
       <c r="R25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.1128142234959393E-2</v>
       </c>
     </row>
@@ -2507,51 +2537,51 @@
         <v>105630.649058576</v>
       </c>
       <c r="G26">
-        <f>F26/(E26)</f>
+        <f t="shared" si="0"/>
         <v>1145.5245515615532</v>
       </c>
       <c r="H26">
-        <f>D26/G26</f>
+        <f t="shared" si="1"/>
         <v>39.008865437395031</v>
       </c>
       <c r="I26">
-        <f>C26/G26</f>
+        <f t="shared" si="2"/>
         <v>53.202732222893005</v>
       </c>
-      <c r="J26" s="5">
-        <f>(E26-E25)/E25</f>
+      <c r="J26">
+        <f t="shared" si="3"/>
         <v>3.6229596001823654E-3</v>
       </c>
       <c r="K26" s="4">
-        <f>(E26-E22)/E22</f>
+        <f t="shared" si="4"/>
         <v>6.1718146822201279E-3</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.2994920771922596</v>
       </c>
       <c r="M26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.2994920771921215</v>
       </c>
       <c r="N26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001381</v>
       </c>
       <c r="O26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1996-1</v>
       </c>
       <c r="P26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.4192038963664047E-2</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-8.0202242814430662E-3</v>
       </c>
       <c r="R26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6.1718146822200559E-3</v>
       </c>
     </row>
@@ -2575,51 +2605,51 @@
         <v>106798.651404466</v>
       </c>
       <c r="G27">
-        <f>F27/(E27)</f>
+        <f t="shared" si="0"/>
         <v>1153.7798625033788</v>
       </c>
       <c r="H27">
-        <f>D27/G27</f>
+        <f t="shared" si="1"/>
         <v>42.746874893040697</v>
       </c>
       <c r="I27">
-        <f>C27/G27</f>
+        <f t="shared" si="2"/>
         <v>49.817274365677164</v>
       </c>
-      <c r="J27" s="5">
-        <f>(E27-E26)/E26</f>
+      <c r="J27">
+        <f t="shared" si="3"/>
         <v>3.8232891238769566E-3</v>
       </c>
       <c r="K27" s="4">
-        <f>(E27-E23)/E23</f>
+        <f t="shared" si="4"/>
         <v>9.1869929239006727E-3</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.0505568733772055</v>
       </c>
       <c r="M27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-5.0556873377095954E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001095</v>
       </c>
       <c r="O27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1996-2</v>
       </c>
       <c r="P27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>9.6514585618716012E-3</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.6446563796992283E-4</v>
       </c>
       <c r="R27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>9.1869929239005721E-3</v>
       </c>
     </row>
@@ -2643,51 +2673,51 @@
         <v>105562.178742319</v>
       </c>
       <c r="G28">
-        <f>F28/(E28)</f>
+        <f t="shared" si="0"/>
         <v>1147.2826860005321</v>
       </c>
       <c r="H28">
-        <f>D28/G28</f>
+        <f t="shared" si="1"/>
         <v>42.802479116697157</v>
       </c>
       <c r="I28">
-        <f>C28/G28</f>
+        <f t="shared" si="2"/>
         <v>49.208129977660207</v>
       </c>
-      <c r="J28" s="5">
-        <f>(E28-E27)/E27</f>
+      <c r="J28">
+        <f t="shared" si="3"/>
         <v>-5.9800707811169685E-3</v>
       </c>
       <c r="K28" s="4">
-        <f>(E28-E24)/E24</f>
+        <f t="shared" si="4"/>
         <v>-1.8273221842254788E-3</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.8306520557353025</v>
       </c>
       <c r="M28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.83065205573838186</v>
       </c>
       <c r="N28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999692069</v>
       </c>
       <c r="O28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1996-3</v>
       </c>
       <c r="P28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-3.3451911130430961E-3</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.5178689288232441E-3</v>
       </c>
       <c r="R28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.8273221842254328E-3</v>
       </c>
     </row>
@@ -2711,51 +2741,51 @@
         <v>108890.348796437</v>
       </c>
       <c r="G29">
-        <f>F29/(E29)</f>
+        <f t="shared" si="0"/>
         <v>1189.8154987271766</v>
       </c>
       <c r="H29">
-        <f>D29/G29</f>
+        <f t="shared" si="1"/>
         <v>40.290389779608788</v>
       </c>
       <c r="I29">
-        <f>C29/G29</f>
+        <f t="shared" si="2"/>
         <v>51.228294346564041</v>
       </c>
-      <c r="J29" s="5">
-        <f>(E29-E28)/E28</f>
+      <c r="J29">
+        <f t="shared" si="3"/>
         <v>-5.3463939976750021E-3</v>
       </c>
       <c r="K29" s="4">
-        <f>(E29-E25)/E25</f>
+        <f t="shared" si="4"/>
         <v>-3.9186506690388496E-3</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.86202369116005195</v>
       </c>
       <c r="M29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.13797630883825085</v>
       </c>
       <c r="N29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.9999999999983028</v>
       </c>
       <c r="O29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1996-4</v>
       </c>
       <c r="P29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-3.3779697140916762E-3</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-5.4068095494052258E-4</v>
       </c>
       <c r="R29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.9186506690388478E-3</v>
       </c>
     </row>
@@ -2779,51 +2809,51 @@
         <v>105123.232566288</v>
       </c>
       <c r="G30">
-        <f>F30/(E30)</f>
+        <f t="shared" si="0"/>
         <v>1143.2796221359422</v>
       </c>
       <c r="H30">
-        <f>D30/G30</f>
+        <f t="shared" si="1"/>
         <v>39.167150482586699</v>
       </c>
       <c r="I30">
-        <f>C30/G30</f>
+        <f t="shared" si="2"/>
         <v>52.781687344060558</v>
       </c>
-      <c r="J30" s="5">
-        <f>(E30-E29)/E29</f>
+      <c r="J30">
+        <f t="shared" si="3"/>
         <v>4.700173572003712E-3</v>
       </c>
       <c r="K30" s="4">
-        <f>(E30-E26)/E26</f>
+        <f t="shared" si="4"/>
         <v>-2.8495312987551892E-3</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.60239437283173303</v>
       </c>
       <c r="M30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.6023943728300836</v>
       </c>
       <c r="N30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999835054</v>
       </c>
       <c r="O30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1997-1</v>
       </c>
       <c r="P30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.7165416195780259E-3</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.5660729183285148E-3</v>
       </c>
       <c r="R30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-2.8495312987552035E-3</v>
       </c>
     </row>
@@ -2847,51 +2877,51 @@
         <v>107801.777831809</v>
       </c>
       <c r="G31">
-        <f>F31/(E31)</f>
+        <f t="shared" si="0"/>
         <v>1175.0657665302433</v>
       </c>
       <c r="H31">
-        <f>D31/G31</f>
+        <f t="shared" si="1"/>
         <v>40.709643246605573</v>
       </c>
       <c r="I31">
-        <f>C31/G31</f>
+        <f t="shared" si="2"/>
         <v>51.031415766736188</v>
       </c>
-      <c r="J31" s="5">
-        <f>(E31-E30)/E30</f>
+      <c r="J31">
+        <f t="shared" si="3"/>
         <v>-2.2597220173323717E-3</v>
       </c>
       <c r="K31" s="4">
-        <f>(E31-E27)/E27</f>
+        <f t="shared" si="4"/>
         <v>-8.8921061984328156E-3</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.4751011907621625</v>
       </c>
       <c r="M31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.4751011907621712</v>
       </c>
       <c r="N31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999999134</v>
       </c>
       <c r="O31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1997-2</v>
       </c>
       <c r="P31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.2008862640124669E-2</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.311675644169193E-2</v>
       </c>
       <c r="R31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-8.8921061984328365E-3</v>
       </c>
     </row>
@@ -2915,51 +2945,51 @@
         <v>108474.32851150499</v>
       </c>
       <c r="G32">
-        <f>F32/(E32)</f>
+        <f t="shared" si="0"/>
         <v>1182.9140042731287</v>
       </c>
       <c r="H32">
-        <f>D32/G32</f>
+        <f t="shared" si="1"/>
         <v>42.559758895855445</v>
       </c>
       <c r="I32">
-        <f>C32/G32</f>
+        <f t="shared" si="2"/>
         <v>49.141183116543971</v>
       </c>
-      <c r="J32" s="5">
-        <f>(E32-E31)/E31</f>
+      <c r="J32">
+        <f t="shared" si="3"/>
         <v>-4.3728513028245332E-4</v>
       </c>
       <c r="K32" s="4">
-        <f>(E32-E28)/E28</f>
+        <f t="shared" si="4"/>
         <v>-3.3655584394668299E-3</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.78381021097564973</v>
       </c>
       <c r="M32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.2161897890241897</v>
       </c>
       <c r="N32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999983946</v>
       </c>
       <c r="O32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1997-3</v>
       </c>
       <c r="P32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.6379590704893744E-3</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-7.275993689769151E-4</v>
       </c>
       <c r="R32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.3655584394668425E-3</v>
       </c>
     </row>
@@ -2983,51 +3013,51 @@
         <v>112348.15315963099</v>
       </c>
       <c r="G33">
-        <f>F33/(E33)</f>
+        <f t="shared" si="0"/>
         <v>1232.3971679919464</v>
       </c>
       <c r="H33">
-        <f>D33/G33</f>
+        <f t="shared" si="1"/>
         <v>42.331865513993478</v>
       </c>
       <c r="I33">
-        <f>C33/G33</f>
+        <f t="shared" si="2"/>
         <v>48.830428653470229</v>
       </c>
-      <c r="J33" s="5">
-        <f>(E33-E32)/E32</f>
+      <c r="J33">
+        <f t="shared" si="3"/>
         <v>-5.8739619584558412E-3</v>
       </c>
       <c r="K33" s="4">
-        <f>(E33-E29)/E29</f>
+        <f t="shared" si="4"/>
         <v>-3.8941770427726443E-3</v>
       </c>
       <c r="L33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-5.7282077805456826</v>
       </c>
       <c r="M33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6.7282077805463008</v>
       </c>
       <c r="N33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000006182</v>
       </c>
       <c r="O33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1997-4</v>
       </c>
       <c r="P33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.2306655235232637E-2</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-2.620083227800769E-2</v>
       </c>
       <c r="R33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.8941770427726174E-3</v>
       </c>
     </row>
@@ -3051,51 +3081,51 @@
         <v>109152.280583389</v>
       </c>
       <c r="G34">
-        <f>F34/(E34)</f>
+        <f t="shared" ref="G34:G65" si="12">F34/(E34)</f>
         <v>1188.8422943369997</v>
       </c>
       <c r="H34">
-        <f>D34/G34</f>
+        <f t="shared" ref="H34:H65" si="13">D34/G34</f>
         <v>38.868943869367399</v>
       </c>
       <c r="I34">
-        <f>C34/G34</f>
+        <f t="shared" ref="I34:I65" si="14">C34/G34</f>
         <v>52.944983935296683</v>
       </c>
-      <c r="J34" s="5">
-        <f>(E34-E33)/E33</f>
+      <c r="J34">
+        <f t="shared" si="3"/>
         <v>7.1480609735836836E-3</v>
       </c>
       <c r="K34" s="4">
-        <f>(E34-E30)/E30</f>
+        <f t="shared" si="4"/>
         <v>-1.4672292241130933E-3</v>
       </c>
       <c r="L34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.2104111231854948</v>
       </c>
       <c r="M34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.2104111231804389</v>
       </c>
       <c r="N34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.000000000005056</v>
       </c>
       <c r="O34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1998-1</v>
       </c>
       <c r="P34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-3.2431797972424046E-3</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.7759505731218931E-3</v>
       </c>
       <c r="R34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.4672292241131313E-3</v>
       </c>
     </row>
@@ -3119,51 +3149,51 @@
         <v>111610.928783956</v>
       </c>
       <c r="G35">
-        <f>F35/(E35)</f>
+        <f t="shared" si="12"/>
         <v>1217.8095239592719</v>
       </c>
       <c r="H35">
-        <f>D35/G35</f>
+        <f t="shared" si="13"/>
         <v>41.851154978650406</v>
       </c>
       <c r="I35">
-        <f>C35/G35</f>
+        <f t="shared" si="14"/>
         <v>49.797765963511928</v>
       </c>
-      <c r="J35" s="5">
-        <f>(E35-E34)/E34</f>
+      <c r="J35">
+        <f t="shared" ref="J35:J66" si="15">(E35-E34)/E34</f>
         <v>-1.7971877083066525E-3</v>
       </c>
       <c r="K35" s="4">
-        <f>(E35-E31)/E31</f>
+        <f t="shared" si="4"/>
         <v>-1.0043275297922146E-3</v>
       </c>
       <c r="L35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-12.389142918157312</v>
       </c>
       <c r="M35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>13.389142918157699</v>
       </c>
       <c r="N35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000003872</v>
       </c>
       <c r="O35" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1998-2</v>
       </c>
       <c r="P35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.2442757303235642E-2</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.3447084833028245E-2</v>
       </c>
       <c r="R35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.0043275297921817E-3</v>
       </c>
     </row>
@@ -3187,51 +3217,51 @@
         <v>110834.936418433</v>
       </c>
       <c r="G36">
-        <f>F36/(E36)</f>
+        <f t="shared" si="12"/>
         <v>1210.2342415594187</v>
       </c>
       <c r="H36">
-        <f>D36/G36</f>
+        <f t="shared" si="13"/>
         <v>44.066569930346766</v>
       </c>
       <c r="I36">
-        <f>C36/G36</f>
+        <f t="shared" si="14"/>
         <v>47.514822012108581</v>
       </c>
-      <c r="J36" s="5">
-        <f>(E36-E35)/E35</f>
+      <c r="J36">
+        <f t="shared" si="15"/>
         <v>-7.3682263809872223E-4</v>
       </c>
       <c r="K36" s="4">
-        <f>(E36-E32)/E32</f>
+        <f t="shared" si="4"/>
         <v>-1.3036951128357318E-3</v>
       </c>
       <c r="L36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-12.604016335558622</v>
       </c>
       <c r="M36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>13.604016335559217</v>
       </c>
       <c r="N36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000005951</v>
       </c>
       <c r="O36" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1998-3</v>
       </c>
       <c r="P36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.6431794498769504E-2</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.7735489611606012E-2</v>
       </c>
       <c r="R36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.3036951128356788E-3</v>
       </c>
     </row>
@@ -3255,51 +3285,51 @@
         <v>113356.69703215999</v>
       </c>
       <c r="G37">
-        <f>F37/(E37)</f>
+        <f t="shared" si="12"/>
         <v>1248.1821927989668</v>
       </c>
       <c r="H37">
-        <f>D37/G37</f>
+        <f t="shared" si="13"/>
         <v>41.333766116563623</v>
       </c>
       <c r="I37">
-        <f>C37/G37</f>
+        <f t="shared" si="14"/>
         <v>49.483662369549087</v>
       </c>
-      <c r="J37" s="5">
-        <f>(E37-E36)/E36</f>
+      <c r="J37">
+        <f t="shared" si="15"/>
         <v>-8.3419070199547921E-3</v>
       </c>
       <c r="K37" s="4">
-        <f>(E37-E33)/E33</f>
+        <f t="shared" si="4"/>
         <v>-3.7829859866962637E-3</v>
       </c>
       <c r="L37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.8941685166265221</v>
       </c>
       <c r="M37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.8941685166253683</v>
       </c>
       <c r="N37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000011537</v>
       </c>
       <c r="O37" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1998-4</v>
       </c>
       <c r="P37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-1.0948598941535645E-2</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7.1656129548350175E-3</v>
       </c>
       <c r="R37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.7829859866962412E-3</v>
       </c>
     </row>
@@ -3323,51 +3353,51 @@
         <v>109865.535989258</v>
       </c>
       <c r="G38">
-        <f>F38/(E38)</f>
+        <f t="shared" si="12"/>
         <v>1200.1984771682262</v>
       </c>
       <c r="H38">
-        <f>D38/G38</f>
+        <f t="shared" si="13"/>
         <v>36.634163753644842</v>
       </c>
       <c r="I38">
-        <f>C38/G38</f>
+        <f t="shared" si="14"/>
         <v>54.905309157933459</v>
       </c>
-      <c r="J38" s="5">
-        <f>(E38-E37)/E37</f>
+      <c r="J38">
+        <f t="shared" si="15"/>
         <v>7.9505050682569019E-3</v>
       </c>
       <c r="K38" s="4">
-        <f>(E38-E34)/E34</f>
+        <f t="shared" ref="K38:K69" si="16">(E38-E34)/E34</f>
         <v>-2.9892511915012095E-3</v>
       </c>
       <c r="L38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8.1426134932060634</v>
       </c>
       <c r="M38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-7.1426134932086782</v>
       </c>
       <c r="N38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.9999999999973852</v>
       </c>
       <c r="O38" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1999-1</v>
       </c>
       <c r="P38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.434031708650005E-2</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.1351065895006658E-2</v>
       </c>
       <c r="R38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-2.9892511915011744E-3</v>
       </c>
     </row>
@@ -3391,51 +3421,51 @@
         <v>111559.731776054</v>
       </c>
       <c r="G39">
-        <f>F39/(E39)</f>
+        <f t="shared" si="12"/>
         <v>1221.1180343854132</v>
       </c>
       <c r="H39">
-        <f>D39/G39</f>
+        <f t="shared" si="13"/>
         <v>41.608909234598627</v>
       </c>
       <c r="I39">
-        <f>C39/G39</f>
+        <f t="shared" si="14"/>
         <v>49.749770790303458</v>
       </c>
-      <c r="J39" s="5">
-        <f>(E39-E38)/E38</f>
+      <c r="J39">
+        <f t="shared" si="15"/>
         <v>-1.9750265205354302E-3</v>
       </c>
       <c r="K39" s="4">
-        <f>(E39-E35)/E35</f>
+        <f t="shared" si="16"/>
         <v>-3.1668776268949975E-3</v>
       </c>
       <c r="L39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.83463677808771186</v>
       </c>
       <c r="M39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.16536322191037858</v>
       </c>
       <c r="N39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999809042</v>
       </c>
       <c r="O39" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1999-2</v>
       </c>
       <c r="P39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.6431925391096995E-3</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-5.2368508777925064E-4</v>
       </c>
       <c r="R39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.1668776268950483E-3</v>
       </c>
     </row>
@@ -3459,51 +3489,51 @@
         <v>112723.231056373</v>
       </c>
       <c r="G40">
-        <f>F40/(E40)</f>
+        <f t="shared" si="12"/>
         <v>1223.6988650001597</v>
       </c>
       <c r="H40">
-        <f>D40/G40</f>
+        <f t="shared" si="13"/>
         <v>43.462036013792137</v>
       </c>
       <c r="I40">
-        <f>C40/G40</f>
+        <f t="shared" si="14"/>
         <v>48.654770073429489</v>
       </c>
-      <c r="J40" s="5">
-        <f>(E40-E39)/E39</f>
+      <c r="J40">
+        <f t="shared" si="15"/>
         <v>8.2983473722831706E-3</v>
       </c>
       <c r="K40" s="4">
-        <f>(E40-E36)/E36</f>
+        <f t="shared" si="16"/>
         <v>5.8463202339513595E-3</v>
       </c>
       <c r="L40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-1.1290959016746833</v>
       </c>
       <c r="M40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.1290959016740727</v>
       </c>
       <c r="N40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999938938</v>
       </c>
       <c r="O40" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1999-3</v>
       </c>
       <c r="P40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-6.6010562160322556E-3</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.2447376449980046E-2</v>
       </c>
       <c r="R40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.8463202339513742E-3</v>
       </c>
     </row>
@@ -3527,51 +3557,51 @@
         <v>119382.608315524</v>
       </c>
       <c r="G41">
-        <f>F41/(E41)</f>
+        <f t="shared" si="12"/>
         <v>1301.7897003021549</v>
       </c>
       <c r="H41">
-        <f>D41/G41</f>
+        <f t="shared" si="13"/>
         <v>44.470848178236025</v>
       </c>
       <c r="I41">
-        <f>C41/G41</f>
+        <f t="shared" si="14"/>
         <v>47.235675761702069</v>
       </c>
-      <c r="J41" s="5">
-        <f>(E41-E40)/E40</f>
+      <c r="J41">
+        <f t="shared" si="15"/>
         <v>-4.4539337034268048E-3</v>
       </c>
       <c r="K41" s="4">
-        <f>(E41-E37)/E37</f>
+        <f t="shared" si="16"/>
         <v>9.7899210387865816E-3</v>
       </c>
       <c r="L41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3.5283973708080048</v>
       </c>
       <c r="M41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-2.5283973708072298</v>
       </c>
       <c r="N41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000007749</v>
       </c>
       <c r="O41" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q1999-4</v>
       </c>
       <c r="P41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>3.4542731653672547E-2</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-2.4752810614878377E-2</v>
       </c>
       <c r="R41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>9.7899210387866198E-3</v>
       </c>
     </row>
@@ -3595,51 +3625,51 @@
         <v>116222.45277930101</v>
       </c>
       <c r="G42">
-        <f>F42/(E42)</f>
+        <f t="shared" si="12"/>
         <v>1254.4805668322779</v>
       </c>
       <c r="H42">
-        <f>D42/G42</f>
+        <f t="shared" si="13"/>
         <v>38.884862827719729</v>
       </c>
       <c r="I42">
-        <f>C42/G42</f>
+        <f t="shared" si="14"/>
         <v>53.761014559426819</v>
       </c>
-      <c r="J42" s="5">
-        <f>(E42-E41)/E41</f>
+      <c r="J42">
+        <f t="shared" si="15"/>
         <v>1.0243038410481277E-2</v>
       </c>
       <c r="K42" s="4">
-        <f>(E42-E38)/E38</f>
+        <f t="shared" si="16"/>
         <v>1.2086638041241748E-2</v>
       </c>
       <c r="L42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2.0342461764887849</v>
       </c>
       <c r="M42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.0342461764888298</v>
       </c>
       <c r="N42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999995515</v>
       </c>
       <c r="O42" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2000-1</v>
       </c>
       <c r="P42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.4587197221999924E-2</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.2500559180758717E-2</v>
       </c>
       <c r="R42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.208663804124166E-2</v>
       </c>
     </row>
@@ -3663,51 +3693,51 @@
         <v>117376.007064976</v>
       </c>
       <c r="G43">
-        <f>F43/(E43)</f>
+        <f t="shared" si="12"/>
         <v>1267.2654021564072</v>
       </c>
       <c r="H43">
-        <f>D43/G43</f>
+        <f t="shared" si="13"/>
         <v>42.214188070353302</v>
       </c>
       <c r="I43">
-        <f>C43/G43</f>
+        <f t="shared" si="14"/>
         <v>50.407299792604249</v>
       </c>
-      <c r="J43" s="5">
-        <f>(E43-E42)/E42</f>
+      <c r="J43">
+        <f t="shared" si="15"/>
         <v>-2.6325536414938886E-4</v>
       </c>
       <c r="K43" s="4">
-        <f>(E43-E39)/E39</f>
+        <f t="shared" si="16"/>
         <v>1.3822527183096338E-2</v>
       </c>
       <c r="L43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.47931190915512079</v>
       </c>
       <c r="M43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.52068809084445156</v>
       </c>
       <c r="N43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999957234</v>
       </c>
       <c r="O43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2000-2</v>
       </c>
       <c r="P43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>6.6253018934784597E-3</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7.197225289611967E-3</v>
       </c>
       <c r="R43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.3822527183096289E-2</v>
       </c>
     </row>
@@ -3731,51 +3761,51 @@
         <v>118694.816972498</v>
       </c>
       <c r="G44">
-        <f>F44/(E44)</f>
+        <f t="shared" si="12"/>
         <v>1270.4124750505619</v>
       </c>
       <c r="H44">
-        <f>D44/G44</f>
+        <f t="shared" si="13"/>
         <v>45.529150950654142</v>
       </c>
       <c r="I44">
-        <f>C44/G44</f>
+        <f t="shared" si="14"/>
         <v>47.9009902857767</v>
       </c>
-      <c r="J44" s="5">
-        <f>(E44-E43)/E43</f>
+      <c r="J44">
+        <f t="shared" si="15"/>
         <v>8.7307318434548323E-3</v>
       </c>
       <c r="K44" s="4">
-        <f>(E44-E40)/E40</f>
+        <f t="shared" si="16"/>
         <v>1.4257280565783504E-2</v>
       </c>
       <c r="L44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.5739432071900112</v>
       </c>
       <c r="M44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.57394320719014646</v>
       </c>
       <c r="N44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999986477</v>
       </c>
       <c r="O44" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2000-3</v>
       </c>
       <c r="P44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.2440149899517106E-2</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-8.1828693337355311E-3</v>
       </c>
       <c r="R44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.4257280565783459E-2</v>
       </c>
     </row>
@@ -3799,51 +3829,51 @@
         <v>124501.15501546</v>
       </c>
       <c r="G45">
-        <f>F45/(E45)</f>
+        <f t="shared" si="12"/>
         <v>1334.3747889750457</v>
       </c>
       <c r="H45">
-        <f>D45/G45</f>
+        <f t="shared" si="13"/>
         <v>44.226547716188065</v>
       </c>
       <c r="I45">
-        <f>C45/G45</f>
+        <f t="shared" si="14"/>
         <v>49.076440352921843</v>
       </c>
-      <c r="J45" s="5">
-        <f>(E45-E44)/E44</f>
+      <c r="J45">
+        <f t="shared" si="15"/>
         <v>-1.3609437558188889E-3</v>
       </c>
       <c r="K45" s="4">
-        <f>(E45-E41)/E41</f>
+        <f t="shared" si="16"/>
         <v>1.7408403029405967E-2</v>
       </c>
       <c r="L45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.15302596380578801</v>
       </c>
       <c r="M45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.1530259638054809</v>
       </c>
       <c r="N45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999969291</v>
       </c>
       <c r="O45" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2000-4</v>
       </c>
       <c r="P45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.6639376518944476E-3</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.007234068129507E-2</v>
       </c>
       <c r="R45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.7408403029405939E-2</v>
       </c>
     </row>
@@ -3867,51 +3897,51 @@
         <v>120982.68959239</v>
       </c>
       <c r="G46">
-        <f>F46/(E46)</f>
+        <f t="shared" si="12"/>
         <v>1282.0678899906525</v>
       </c>
       <c r="H46">
-        <f>D46/G46</f>
+        <f t="shared" si="13"/>
         <v>38.501547512589177</v>
       </c>
       <c r="I46">
-        <f>C46/G46</f>
+        <f t="shared" si="14"/>
         <v>55.863727943511932</v>
       </c>
-      <c r="J46" s="5">
-        <f>(E46-E45)/E45</f>
+      <c r="J46">
+        <f t="shared" si="15"/>
         <v>1.1385352269789694E-2</v>
       </c>
       <c r="K46" s="4">
-        <f>(E46-E42)/E42</f>
+        <f t="shared" si="16"/>
         <v>1.8558818993851454E-2</v>
       </c>
       <c r="L46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.22293575993347986</v>
       </c>
       <c r="M46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.2229357599334552</v>
       </c>
       <c r="N46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999997535</v>
       </c>
       <c r="O46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2001-1</v>
       </c>
       <c r="P46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-4.1374244158621743E-3</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.2696243409713168E-2</v>
       </c>
       <c r="R46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.8558818993851478E-2</v>
       </c>
     </row>
@@ -3935,51 +3965,51 @@
         <v>121914.544714638</v>
       </c>
       <c r="G47">
-        <f>F47/(E47)</f>
+        <f t="shared" si="12"/>
         <v>1298.7208160387872</v>
       </c>
       <c r="H47">
-        <f>D47/G47</f>
+        <f t="shared" si="13"/>
         <v>43.720108057314917</v>
       </c>
       <c r="I47">
-        <f>C47/G47</f>
+        <f t="shared" si="14"/>
         <v>50.152680619845562</v>
       </c>
-      <c r="J47" s="5">
-        <f>(E47-E46)/E46</f>
+      <c r="J47">
+        <f t="shared" si="15"/>
         <v>-5.2189407232738697E-3</v>
       </c>
       <c r="K47" s="4">
-        <f>(E47-E43)/E43</f>
+        <f t="shared" si="16"/>
         <v>1.3509832794455997E-2</v>
       </c>
       <c r="L47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.2034835827399661</v>
       </c>
       <c r="M47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.20348358273946066</v>
       </c>
       <c r="N47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000005054</v>
       </c>
       <c r="O47" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2001-2</v>
       </c>
       <c r="P47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.6258861973689791E-2</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-2.7490291792269658E-3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.3509832794456056E-2</v>
       </c>
     </row>
@@ -4003,51 +4033,51 @@
         <v>121598.274711501</v>
       </c>
       <c r="G48">
-        <f>F48/(E48)</f>
+        <f t="shared" si="12"/>
         <v>1291.1567318413586</v>
       </c>
       <c r="H48">
-        <f>D48/G48</f>
+        <f t="shared" si="13"/>
         <v>43.405749495539006</v>
       </c>
       <c r="I48">
-        <f>C48/G48</f>
+        <f t="shared" si="14"/>
         <v>50.772030562259069</v>
       </c>
-      <c r="J48" s="5">
-        <f>(E48-E47)/E47</f>
+      <c r="J48">
+        <f t="shared" si="15"/>
         <v>3.2489860473518292E-3</v>
       </c>
       <c r="K48" s="4">
-        <f>(E48-E44)/E44</f>
+        <f t="shared" si="16"/>
         <v>8.0021159282544097E-3</v>
       </c>
       <c r="L48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-2.8401433879963105</v>
       </c>
       <c r="M48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8401433879964815</v>
       </c>
       <c r="N48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.000000000000171</v>
       </c>
       <c r="O48" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2001-3</v>
       </c>
       <c r="P48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.2727156643611721E-2</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.07292725718675E-2</v>
       </c>
       <c r="R48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.0021159282543941E-3</v>
       </c>
     </row>
@@ -4071,51 +4101,51 @@
         <v>125178.746630886</v>
       </c>
       <c r="G49">
-        <f>F49/(E49)</f>
+        <f t="shared" si="12"/>
         <v>1336.212340318167</v>
       </c>
       <c r="H49">
-        <f>D49/G49</f>
+        <f t="shared" si="13"/>
         <v>41.303213248729001</v>
       </c>
       <c r="I49">
-        <f>C49/G49</f>
+        <f t="shared" si="14"/>
         <v>52.378563856457326</v>
       </c>
-      <c r="J49" s="5">
-        <f>(E49-E48)/E48</f>
+      <c r="J49">
+        <f t="shared" si="15"/>
         <v>-5.2666664292511422E-3</v>
       </c>
       <c r="K49" s="4">
-        <f>(E49-E45)/E45</f>
+        <f t="shared" si="16"/>
         <v>4.0597739034437703E-3</v>
       </c>
       <c r="L49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-7.7175794150235726</v>
       </c>
       <c r="M49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>8.7175794150238914</v>
       </c>
       <c r="N49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000003189</v>
       </c>
       <c r="O49" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2001-4</v>
       </c>
       <c r="P49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-3.1331627506867542E-2</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.5391401410312606E-2</v>
       </c>
       <c r="R49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.0597739034438085E-3</v>
       </c>
     </row>
@@ -4139,51 +4169,51 @@
         <v>120513.212210029</v>
       </c>
       <c r="G50">
-        <f>F50/(E50)</f>
+        <f t="shared" si="12"/>
         <v>1284.7232066939566</v>
       </c>
       <c r="H50">
-        <f>D50/G50</f>
+        <f t="shared" si="13"/>
         <v>31.967046282185148</v>
       </c>
       <c r="I50">
-        <f>C50/G50</f>
+        <f t="shared" si="14"/>
         <v>61.837760529199137</v>
       </c>
-      <c r="J50" s="5">
-        <f>(E50-E49)/E49</f>
+      <c r="J50">
+        <f t="shared" si="15"/>
         <v>1.3132725488326066E-3</v>
       </c>
       <c r="K50" s="4">
-        <f>(E50-E46)/E46</f>
+        <f t="shared" si="16"/>
         <v>-5.9393526062152032E-3</v>
       </c>
       <c r="L50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>11.658995185556583</v>
       </c>
       <c r="M50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-10.65899518555584</v>
       </c>
       <c r="N50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000007425</v>
       </c>
       <c r="O50" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2002-1</v>
       </c>
       <c r="P50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-6.9246883441186E-2</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6.3307530834966388E-2</v>
       </c>
       <c r="R50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-5.9393526062152535E-3</v>
       </c>
     </row>
@@ -4207,51 +4237,51 @@
         <v>122115.698360165</v>
       </c>
       <c r="G51">
-        <f>F51/(E51)</f>
+        <f t="shared" si="12"/>
         <v>1307.2101252176763</v>
       </c>
       <c r="H51">
-        <f>D51/G51</f>
+        <f t="shared" si="13"/>
         <v>41.575359781334299</v>
       </c>
       <c r="I51">
-        <f>C51/G51</f>
+        <f t="shared" si="14"/>
         <v>51.841678538981782</v>
       </c>
-      <c r="J51" s="5">
-        <f>(E51-E50)/E50</f>
+      <c r="J51">
+        <f t="shared" si="15"/>
         <v>-4.1337806051665905E-3</v>
       </c>
       <c r="K51" s="4">
-        <f>(E51-E47)/E47</f>
+        <f t="shared" si="16"/>
         <v>-4.8549783517275501E-3</v>
       </c>
       <c r="L51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>4.7059716877307576</v>
       </c>
       <c r="M51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-3.7059716877296816</v>
       </c>
       <c r="N51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.000000000001076</v>
       </c>
       <c r="O51" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2002-2</v>
       </c>
       <c r="P51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-2.284739066777559E-2</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.7992412316042816E-2</v>
       </c>
       <c r="R51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-4.8549783517275458E-3</v>
       </c>
     </row>
@@ -4275,51 +4305,51 @@
         <v>121806.73065210901</v>
       </c>
       <c r="G52">
-        <f>F52/(E52)</f>
+        <f t="shared" si="12"/>
         <v>1301.6054902300068</v>
       </c>
       <c r="H52">
-        <f>D52/G52</f>
+        <f t="shared" si="13"/>
         <v>43.354509363684812</v>
       </c>
       <c r="I52">
-        <f>C52/G52</f>
+        <f t="shared" si="14"/>
         <v>50.227402795109334</v>
       </c>
-      <c r="J52" s="5">
-        <f>(E52-E51)/E51</f>
+      <c r="J52">
+        <f t="shared" si="15"/>
         <v>1.7649225606239775E-3</v>
       </c>
       <c r="K52" s="4">
-        <f>(E52-E48)/E48</f>
+        <f t="shared" si="16"/>
         <v>-6.3270539891481228E-3</v>
       </c>
       <c r="L52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8.5992435470778644E-2</v>
       </c>
       <c r="M52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.91400756452942411</v>
       </c>
       <c r="N52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000002027</v>
       </c>
       <c r="O52" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2002-3</v>
       </c>
       <c r="P52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-5.4407878188195255E-4</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-5.7829752072674533E-3</v>
       </c>
       <c r="R52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-6.3270539891481237E-3</v>
       </c>
     </row>
@@ -4343,51 +4373,51 @@
         <v>124857.15596310201</v>
       </c>
       <c r="G53">
-        <f>F53/(E53)</f>
+        <f t="shared" si="12"/>
         <v>1334.4313200529989</v>
       </c>
       <c r="H53">
-        <f>D53/G53</f>
+        <f t="shared" si="13"/>
         <v>43.026838900624611</v>
       </c>
       <c r="I53">
-        <f>C53/G53</f>
+        <f t="shared" si="14"/>
         <v>50.538977553790851</v>
       </c>
-      <c r="J53" s="5">
-        <f>(E53-E52)/E52</f>
+      <c r="J53">
+        <f t="shared" si="15"/>
         <v>-1.7199589116949501E-4</v>
       </c>
       <c r="K53" s="4">
-        <f>(E53-E49)/E49</f>
+        <f t="shared" si="16"/>
         <v>-1.2378143792137841E-3</v>
       </c>
       <c r="L53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-14.863883916087593</v>
       </c>
       <c r="M53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>15.863883916085571</v>
       </c>
       <c r="N53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999797851</v>
       </c>
       <c r="O53" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2002-4</v>
       </c>
       <c r="P53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.8398729242297716E-2</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.9636543621508996E-2</v>
       </c>
       <c r="R53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.2378143792137752E-3</v>
       </c>
     </row>
@@ -4411,51 +4441,51 @@
         <v>120846.28343501499</v>
       </c>
       <c r="G54">
-        <f>F54/(E54)</f>
+        <f t="shared" si="12"/>
         <v>1278.9534531607699</v>
       </c>
       <c r="H54">
-        <f>D54/G54</f>
+        <f t="shared" si="13"/>
         <v>32.805545566095354</v>
       </c>
       <c r="I54">
-        <f>C54/G54</f>
+        <f t="shared" si="14"/>
         <v>61.682868485533582</v>
       </c>
-      <c r="J54" s="5">
-        <f>(E54-E53)/E53</f>
+      <c r="J54">
+        <f t="shared" si="15"/>
         <v>9.860413045856135E-3</v>
       </c>
       <c r="K54" s="4">
-        <f>(E54-E50)/E50</f>
+        <f t="shared" si="16"/>
         <v>7.2875502171082284E-3</v>
       </c>
       <c r="L54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.2265804610419242</v>
       </c>
       <c r="M54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.22658046104111856</v>
       </c>
       <c r="N54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000008056</v>
       </c>
       <c r="O54" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2003-1</v>
       </c>
       <c r="P54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>8.9387667051667851E-3</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.651216488052686E-3</v>
       </c>
       <c r="R54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.2875502171081408E-3</v>
       </c>
     </row>
@@ -4479,51 +4509,51 @@
         <v>122079.39943012</v>
       </c>
       <c r="G55">
-        <f>F55/(E55)</f>
+        <f t="shared" si="12"/>
         <v>1288.2804776400412</v>
       </c>
       <c r="H55">
-        <f>D55/G55</f>
+        <f t="shared" si="13"/>
         <v>42.44513058706022</v>
       </c>
       <c r="I55">
-        <f>C55/G55</f>
+        <f t="shared" si="14"/>
         <v>52.316376358813024</v>
       </c>
-      <c r="J55" s="5">
-        <f>(E55-E54)/E54</f>
+      <c r="J55">
+        <f t="shared" si="15"/>
         <v>2.8902262461056104E-3</v>
       </c>
       <c r="K55" s="4">
-        <f>(E55-E51)/E51</f>
+        <f t="shared" si="16"/>
         <v>1.4392113577260763E-2</v>
       </c>
       <c r="L55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.64692532736893094</v>
       </c>
       <c r="M55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.35307467263095804</v>
       </c>
       <c r="N55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999988898</v>
       </c>
       <c r="O55" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2003-2</v>
       </c>
       <c r="P55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>9.3106227875002553E-3</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5.0814907897589103E-3</v>
       </c>
       <c r="R55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.4392113577260668E-2</v>
       </c>
     </row>
@@ -4547,51 +4577,51 @@
         <v>122722.691285368</v>
       </c>
       <c r="G56">
-        <f>F56/(E56)</f>
+        <f t="shared" si="12"/>
         <v>1295.0638982880928</v>
       </c>
       <c r="H56">
-        <f>D56/G56</f>
+        <f t="shared" si="13"/>
         <v>43.465086995009806</v>
       </c>
       <c r="I56">
-        <f>C56/G56</f>
+        <f t="shared" si="14"/>
         <v>51.296794212235199</v>
       </c>
-      <c r="J56" s="5">
-        <f>(E56-E55)/E55</f>
+      <c r="J56">
+        <f t="shared" si="15"/>
         <v>3.9495084412682084E-6</v>
       </c>
       <c r="K56" s="4">
-        <f>(E56-E52)/E52</f>
+        <f t="shared" si="16"/>
         <v>1.2608943557901141E-2</v>
       </c>
       <c r="L56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>9.3712315140962135E-2</v>
       </c>
       <c r="M56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.90628768485917033</v>
       </c>
       <c r="N56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000001326</v>
       </c>
       <c r="O56" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2003-3</v>
       </c>
       <c r="P56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.181613292292636E-3</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.1427330265610176E-2</v>
       </c>
       <c r="R56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2608943557901098E-2</v>
       </c>
     </row>
@@ -4615,51 +4645,51 @@
         <v>128003.30114654401</v>
       </c>
       <c r="G57">
-        <f>F57/(E57)</f>
+        <f t="shared" si="12"/>
         <v>1350.8132480424745</v>
       </c>
       <c r="H57">
-        <f>D57/G57</f>
+        <f t="shared" si="13"/>
         <v>44.196015446946539</v>
       </c>
       <c r="I57">
-        <f>C57/G57</f>
+        <f t="shared" si="14"/>
         <v>50.56416056705072</v>
       </c>
-      <c r="J57" s="5">
-        <f>(E57-E56)/E56</f>
+      <c r="J57">
+        <f t="shared" si="15"/>
         <v>-1.7994506084897585E-5</v>
       </c>
       <c r="K57" s="4">
-        <f>(E57-E53)/E53</f>
+        <f t="shared" si="16"/>
         <v>1.2764913563958296E-2</v>
       </c>
       <c r="L57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.97891504860672984</v>
       </c>
       <c r="M57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.1084951393270206E-2</v>
       </c>
       <c r="N57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O57" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2003-4</v>
       </c>
       <c r="P57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.2495765981922941E-2</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2.6914758203535623E-4</v>
       </c>
       <c r="R57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2764913563958258E-2</v>
       </c>
     </row>
@@ -4683,51 +4713,51 @@
         <v>124908.046924462</v>
       </c>
       <c r="G58">
-        <f>F58/(E58)</f>
+        <f t="shared" si="12"/>
         <v>1313.1135872297018</v>
       </c>
       <c r="H58">
-        <f>D58/G58</f>
+        <f t="shared" si="13"/>
         <v>35.322543020872473</v>
       </c>
       <c r="I58">
-        <f>C58/G58</f>
+        <f t="shared" si="14"/>
         <v>59.801022936572892</v>
       </c>
-      <c r="J58" s="5">
-        <f>(E58-E57)/E57</f>
+      <c r="J58">
+        <f t="shared" si="15"/>
         <v>3.8348382066578416E-3</v>
       </c>
       <c r="K58" s="4">
-        <f>(E58-E54)/E54</f>
+        <f t="shared" si="16"/>
         <v>6.7220083244232589E-3</v>
       </c>
       <c r="L58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>3.9628275247652414</v>
       </c>
       <c r="M58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-2.9628275247655096</v>
       </c>
       <c r="N58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999973177</v>
       </c>
       <c r="O58" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2004-1</v>
       </c>
       <c r="P58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.663815960972557E-2</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.9916151285304114E-2</v>
       </c>
       <c r="R58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6.7220083244232676E-3</v>
       </c>
     </row>
@@ -4751,51 +4781,51 @@
         <v>126802.201689576</v>
       </c>
       <c r="G59">
-        <f>F59/(E59)</f>
+        <f t="shared" si="12"/>
         <v>1333.0094437581442</v>
       </c>
       <c r="H59">
-        <f>D59/G59</f>
+        <f t="shared" si="13"/>
         <v>44.572302847863703</v>
       </c>
       <c r="I59">
-        <f>C59/G59</f>
+        <f t="shared" si="14"/>
         <v>50.552455857583709</v>
       </c>
-      <c r="J59" s="5">
-        <f>(E59-E58)/E58</f>
+      <c r="J59">
+        <f t="shared" si="15"/>
         <v>1.2538932809195096E-5</v>
       </c>
       <c r="K59" s="4">
-        <f>(E59-E55)/E55</f>
+        <f t="shared" si="16"/>
         <v>3.8333261181809184E-3</v>
       </c>
       <c r="L59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>5.8559172935577211</v>
       </c>
       <c r="M59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-4.8559172935567041</v>
       </c>
       <c r="N59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.000000000001017</v>
       </c>
       <c r="O59" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2004-2</v>
       </c>
       <c r="P59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.2447640707302128E-2</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.861431458911731E-2</v>
       </c>
       <c r="R59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.8333261181808798E-3</v>
       </c>
     </row>
@@ -4819,51 +4849,51 @@
         <v>125978.38507971</v>
       </c>
       <c r="G60">
-        <f>F60/(E60)</f>
+        <f t="shared" si="12"/>
         <v>1328.329945654468</v>
       </c>
       <c r="H60">
-        <f>D60/G60</f>
+        <f t="shared" si="13"/>
         <v>44.105422443160613</v>
       </c>
       <c r="I60">
-        <f>C60/G60</f>
+        <f t="shared" si="14"/>
         <v>50.734256126037614</v>
       </c>
-      <c r="J60" s="5">
-        <f>(E60-E59)/E59</f>
+      <c r="J60">
+        <f t="shared" si="15"/>
         <v>-2.9969078516356939E-3</v>
       </c>
       <c r="K60" s="4">
-        <f>(E60-E56)/E56</f>
+        <f t="shared" si="16"/>
         <v>8.2097739050536586E-4</v>
       </c>
       <c r="L60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8.2308118434459203</v>
       </c>
       <c r="M60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-7.2308118434418098</v>
       </c>
       <c r="N60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000041105</v>
       </c>
       <c r="O60" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2004-3</v>
       </c>
       <c r="P60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>6.7573104289728918E-3</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-5.9363330384641514E-3</v>
       </c>
       <c r="R60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>8.2097739050546181E-4</v>
       </c>
     </row>
@@ -4887,51 +4917,51 @@
         <v>130918.91910842</v>
       </c>
       <c r="G61">
-        <f>F61/(E61)</f>
+        <f t="shared" si="12"/>
         <v>1373.5175801146213</v>
       </c>
       <c r="H61">
-        <f>D61/G61</f>
+        <f t="shared" si="13"/>
         <v>44.118527419975749</v>
       </c>
       <c r="I61">
-        <f>C61/G61</f>
+        <f t="shared" si="14"/>
         <v>51.197994919326426</v>
       </c>
-      <c r="J61" s="5">
-        <f>(E61-E60)/E60</f>
+      <c r="J61">
+        <f t="shared" si="15"/>
         <v>5.0278931487159608E-3</v>
       </c>
       <c r="K61" s="4">
-        <f>(E61-E57)/E57</f>
+        <f t="shared" si="16"/>
         <v>5.8710984794205093E-3</v>
       </c>
       <c r="L61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.13928019912462761</v>
       </c>
       <c r="M61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.1392801991237591</v>
       </c>
       <c r="N61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999913147</v>
       </c>
       <c r="O61" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2004-4</v>
       </c>
       <c r="P61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-8.177277652939869E-4</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6.688826244709397E-3</v>
       </c>
       <c r="R61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.8710984794205778E-3</v>
       </c>
     </row>
@@ -4955,51 +4985,51 @@
         <v>127721.089383484</v>
       </c>
       <c r="G62">
-        <f>F62/(E62)</f>
+        <f t="shared" si="12"/>
         <v>1335.2782277894398</v>
       </c>
       <c r="H62">
-        <f>D62/G62</f>
+        <f t="shared" si="13"/>
         <v>35.759647694523665</v>
       </c>
       <c r="I62">
-        <f>C62/G62</f>
+        <f t="shared" si="14"/>
         <v>59.891645590567059</v>
       </c>
-      <c r="J62" s="5">
-        <f>(E62-E61)/E61</f>
+      <c r="J62">
+        <f t="shared" si="15"/>
         <v>3.5122026860842435E-3</v>
       </c>
       <c r="K62" s="4">
-        <f>(E62-E58)/E58</f>
+        <f t="shared" si="16"/>
         <v>5.547808498702551E-3</v>
       </c>
       <c r="L62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.82827750384139109</v>
       </c>
       <c r="M62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.17172249615813764</v>
       </c>
       <c r="N62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999952871</v>
       </c>
       <c r="O62" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2005-1</v>
       </c>
       <c r="P62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>4.5951249750954045E-3</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9.526835236045322E-4</v>
       </c>
       <c r="R62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.5478084987026222E-3</v>
       </c>
     </row>
@@ -5023,51 +5053,51 @@
         <v>131075.420890899</v>
       </c>
       <c r="G63">
-        <f>F63/(E63)</f>
+        <f t="shared" si="12"/>
         <v>1369.7406440993836</v>
       </c>
       <c r="H63">
-        <f>D63/G63</f>
+        <f t="shared" si="13"/>
         <v>44.102453371874653</v>
       </c>
       <c r="I63">
-        <f>C63/G63</f>
+        <f t="shared" si="14"/>
         <v>51.591152169838786</v>
       </c>
-      <c r="J63" s="5">
-        <f>(E63-E62)/E62</f>
+      <c r="J63">
+        <f t="shared" si="15"/>
         <v>4.4235948275765647E-4</v>
       </c>
       <c r="K63" s="4">
-        <f>(E63-E59)/E59</f>
+        <f t="shared" si="16"/>
         <v>5.9800081914280264E-3</v>
       </c>
       <c r="L63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-0.82596833810847958</v>
       </c>
       <c r="M63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.8259683381081921</v>
       </c>
       <c r="N63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999971256</v>
       </c>
       <c r="O63" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2005-2</v>
       </c>
       <c r="P63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>-4.9392974277489019E-3</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.0919305619175208E-2</v>
       </c>
       <c r="R63">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5.9800081914280767E-3</v>
       </c>
     </row>
@@ -5091,51 +5121,51 @@
         <v>132132.241051152</v>
       </c>
       <c r="G64">
-        <f>F64/(E64)</f>
+        <f t="shared" si="12"/>
         <v>1374.041384352267</v>
       </c>
       <c r="H64">
-        <f>D64/G64</f>
+        <f t="shared" si="13"/>
         <v>45.955131403448917</v>
       </c>
       <c r="I64">
-        <f>C64/G64</f>
+        <f t="shared" si="14"/>
         <v>50.208086499511396</v>
       </c>
-      <c r="J64" s="5">
-        <f>(E64-E63)/E63</f>
+      <c r="J64">
+        <f t="shared" si="15"/>
         <v>4.907458116852924E-3</v>
       </c>
       <c r="K64" s="4">
-        <f>(E64-E60)/E60</f>
+        <f t="shared" si="16"/>
         <v>1.3955544279880739E-2</v>
       </c>
       <c r="L64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.3975474042245437</v>
       </c>
       <c r="M64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.39754740422455453</v>
       </c>
       <c r="N64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999998912</v>
       </c>
       <c r="O64" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2005-3</v>
       </c>
       <c r="P64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.9503534682888006E-2</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-5.5479904030074174E-3</v>
       </c>
       <c r="R64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.3955544279880661E-2</v>
       </c>
     </row>
@@ -5159,51 +5189,51 @@
         <v>137672.40577598201</v>
       </c>
       <c r="G65">
-        <f>F65/(E65)</f>
+        <f t="shared" si="12"/>
         <v>1426.7869314618447</v>
       </c>
       <c r="H65">
-        <f>D65/G65</f>
+        <f t="shared" si="13"/>
         <v>45.577742714424367</v>
       </c>
       <c r="I65">
-        <f>C65/G65</f>
+        <f t="shared" si="14"/>
         <v>50.913473135812652</v>
       </c>
-      <c r="J65" s="5">
-        <f>(E65-E64)/E64</f>
+      <c r="J65">
+        <f t="shared" si="15"/>
         <v>3.4108462094913179E-3</v>
       </c>
       <c r="K65" s="4">
-        <f>(E65-E61)/E61</f>
+        <f t="shared" si="16"/>
         <v>1.2324133131429141E-2</v>
       </c>
       <c r="L65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.2422093770552063</v>
       </c>
       <c r="M65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.24220937705483128</v>
       </c>
       <c r="N65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.000000000000375</v>
       </c>
       <c r="O65" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2005-4</v>
       </c>
       <c r="P65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.5309153739938023E-2</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-2.9850206085042593E-3</v>
       </c>
       <c r="R65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1.2324133131429216E-2</v>
       </c>
     </row>
@@ -5227,51 +5257,51 @@
         <v>136490.87226166</v>
       </c>
       <c r="G66">
-        <f>F66/(E66)</f>
+        <f t="shared" ref="G66:G97" si="17">F66/(E66)</f>
         <v>1398.4434552945652</v>
       </c>
       <c r="H66">
-        <f>D66/G66</f>
+        <f t="shared" ref="H66:H97" si="18">D66/G66</f>
         <v>37.177313669179057</v>
       </c>
       <c r="I66">
-        <f>C66/G66</f>
+        <f t="shared" ref="I66:I97" si="19">C66/G66</f>
         <v>60.424682139017477</v>
       </c>
-      <c r="J66" s="5">
-        <f>(E66-E65)/E65</f>
+      <c r="J66">
+        <f t="shared" si="15"/>
         <v>1.1511721022187539E-2</v>
       </c>
       <c r="K66" s="4">
-        <f>(E66-E62)/E62</f>
+        <f t="shared" si="16"/>
         <v>2.0393895953832973E-2</v>
       </c>
       <c r="L66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.72674636848181906</v>
       </c>
       <c r="M66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.27325363151823556</v>
       </c>
       <c r="N66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000546</v>
       </c>
       <c r="O66" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2006-1</v>
       </c>
       <c r="P66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.4821189823644177E-2</v>
       </c>
       <c r="Q66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5.5727061301899103E-3</v>
       </c>
       <c r="R66">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.0393895953833008E-2</v>
       </c>
     </row>
@@ -5295,51 +5325,51 @@
         <v>139072.706614647</v>
       </c>
       <c r="G67">
-        <f>F67/(E67)</f>
+        <f t="shared" si="17"/>
         <v>1421.3805541687902</v>
       </c>
       <c r="H67">
-        <f>D67/G67</f>
+        <f t="shared" si="18"/>
         <v>46.876069310127811</v>
       </c>
       <c r="I67">
-        <f>C67/G67</f>
+        <f t="shared" si="19"/>
         <v>50.967331042267872</v>
       </c>
-      <c r="J67" s="5">
-        <f>(E67-E66)/E66</f>
+      <c r="J67">
+        <f t="shared" ref="J67:J98" si="20">(E67-E66)/E66</f>
         <v>2.4733566378457796E-3</v>
       </c>
       <c r="K67" s="4">
-        <f>(E67-E63)/E63</f>
+        <f t="shared" si="16"/>
         <v>2.2465396705583417E-2</v>
       </c>
       <c r="L67">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.2901770552571887</v>
       </c>
       <c r="M67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.29017705525717213</v>
       </c>
       <c r="N67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000167</v>
       </c>
       <c r="O67" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2006-2</v>
       </c>
       <c r="P67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.8984339366794162E-2</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-6.5189426612103718E-3</v>
       </c>
       <c r="R67">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.2465396705583451E-2</v>
       </c>
     </row>
@@ -5363,51 +5393,51 @@
         <v>140312.83151768599</v>
       </c>
       <c r="G68">
-        <f>F68/(E68)</f>
+        <f t="shared" si="17"/>
         <v>1428.2055743972351</v>
       </c>
       <c r="H68">
-        <f>D68/G68</f>
+        <f t="shared" si="18"/>
         <v>48.065045198780808</v>
       </c>
       <c r="I68">
-        <f>C68/G68</f>
+        <f t="shared" si="19"/>
         <v>50.179096984254663</v>
       </c>
-      <c r="J68" s="5">
-        <f>(E68-E67)/E67</f>
+      <c r="J68">
+        <f t="shared" si="20"/>
         <v>4.0957471755537732E-3</v>
       </c>
       <c r="K68" s="4">
-        <f>(E68-E64)/E64</f>
+        <f t="shared" si="16"/>
         <v>2.1639503392819098E-2</v>
       </c>
       <c r="L68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.0139310764615292</v>
       </c>
       <c r="M68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-1.3931076461696458E-2</v>
       </c>
       <c r="N68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.9999999999998328</v>
       </c>
       <c r="O68" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2006-3</v>
       </c>
       <c r="P68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.1940964969173981E-2</v>
       </c>
       <c r="Q68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-3.0146157635850275E-4</v>
       </c>
       <c r="R68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.163950339281917E-2</v>
       </c>
     </row>
@@ -5431,51 +5461,51 @@
         <v>146283.22805693501</v>
       </c>
       <c r="G69">
-        <f>F69/(E69)</f>
+        <f t="shared" si="17"/>
         <v>1485.4470880796248</v>
       </c>
       <c r="H69">
-        <f>D69/G69</f>
+        <f t="shared" si="18"/>
         <v>47.989810014573791</v>
       </c>
       <c r="I69">
-        <f>C69/G69</f>
+        <f t="shared" si="19"/>
         <v>50.487765680194741</v>
       </c>
-      <c r="J69" s="5">
-        <f>(E69-E68)/E68</f>
+      <c r="J69">
+        <f t="shared" si="20"/>
         <v>2.3760552695161596E-3</v>
       </c>
       <c r="K69" s="4">
-        <f>(E69-E65)/E65</f>
+        <f t="shared" si="16"/>
         <v>2.0585913723118746E-2</v>
       </c>
       <c r="L69">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.2143153753281599</v>
       </c>
       <c r="M69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-0.21431537532830666</v>
       </c>
       <c r="N69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.99999999999985323</v>
       </c>
       <c r="O69" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2006-4</v>
       </c>
       <c r="P69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2.4997791549162058E-2</v>
       </c>
       <c r="Q69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.4118778260463327E-3</v>
       </c>
       <c r="R69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.0585913723118798E-2</v>
       </c>
     </row>
@@ -5499,51 +5529,51 @@
         <v>144908.386882494</v>
       </c>
       <c r="G70">
-        <f>F70/(E70)</f>
+        <f t="shared" si="17"/>
         <v>1448.3318055163461</v>
       </c>
       <c r="H70">
-        <f>D70/G70</f>
+        <f t="shared" si="18"/>
         <v>38.282430326023416</v>
       </c>
       <c r="I70">
-        <f>C70/G70</f>
+        <f t="shared" si="19"/>
         <v>61.769495849023734</v>
       </c>
-      <c r="J70" s="5">
-        <f>(E70-E69)/E69</f>
+      <c r="J70">
+        <f t="shared" si="20"/>
         <v>1.5986893149746072E-2</v>
       </c>
       <c r="K70" s="4">
-        <f>(E70-E66)/E66</f>
+        <f t="shared" ref="K70:K101" si="21">(E70-E66)/E66</f>
         <v>2.5101232270546999E-2</v>
       </c>
       <c r="L70">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.45108084368334128</v>
       </c>
       <c r="M70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.54891915631670807</v>
       </c>
       <c r="N70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000493</v>
       </c>
       <c r="O70" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Q2007-1</v>
       </c>
       <c r="P70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.1322685030089853E-2</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1.3778547240458384E-2</v>
       </c>
       <c r="R70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>2.5101232270547058E-2</v>
       </c>
     </row>
@@ -5567,51 +5597,51 @@
         <v>148779.38369032301</v>
       </c>
       <c r="G71">
-        <f>F71/(E71)</f>
+        <f t="shared" si="17"/>
         <v>1483.9089674396171</v>
       </c>
       <c r="H71">
-        <f>D71/G71</f>
+        <f t="shared" si="18"/>
         <v>48.155418426452371</v>
       </c>
       <c r="I71">
-        <f>C71/G71</f>
+        <f t="shared" si="19"/>
         <v>52.106381289625723</v>
       </c>
-      <c r="J71" s="5">
-        <f>(E71-E70)/E70</f>
+      <c r="J71">
+        <f t="shared" si="20"/>
         <v>2.0976461828812235E-3</v>
       </c>
       <c r="K71" s="4">
-        <f>(E71-E67)/E67</f>
+        <f t="shared" si="21"/>
         <v>2.4717041261568162E-2</v>
       </c>
       <c r="L71">
-        <f t="shared" ref="L71:L134" si="7">(H71-H67)/(E71-E67)</f>
+        <f t="shared" ref="L71:L134" si="22">(H71-H67)/(E71-E67)</f>
         <v>0.52900655513595607</v>
       </c>
       <c r="M71">
-        <f t="shared" ref="M71:M134" si="8">(I71-I67)/(E71-E67)</f>
+        <f t="shared" ref="M71:M134" si="23">(I71-I67)/(E71-E67)</f>
         <v>0.47099344486409089</v>
       </c>
       <c r="N71">
-        <f t="shared" ref="N71:N134" si="9">M71+L71</f>
+        <f t="shared" ref="N71:N134" si="24">M71+L71</f>
         <v>1.0000000000000471</v>
       </c>
       <c r="O71" t="str">
-        <f t="shared" ref="O71:O134" si="10">"Q"&amp;A71&amp;"-"&amp;B71</f>
+        <f t="shared" ref="O71:O134" si="25">"Q"&amp;A71&amp;"-"&amp;B71</f>
         <v>Q2007-2</v>
       </c>
       <c r="P71">
-        <f t="shared" ref="P71:P134" si="11">L71*K71</f>
+        <f t="shared" ref="P71:P134" si="26">L71*K71</f>
         <v>1.3075476850935458E-2</v>
       </c>
       <c r="Q71">
-        <f t="shared" ref="Q71:Q134" si="12">M71*K71</f>
+        <f t="shared" ref="Q71:Q134" si="27">M71*K71</f>
         <v>1.1641564410633864E-2</v>
       </c>
       <c r="R71">
-        <f t="shared" ref="R71:R134" si="13">E71/E67-1</f>
+        <f t="shared" ref="R71:R134" si="28">E71/E67-1</f>
         <v>2.4717041261568262E-2</v>
       </c>
     </row>
@@ -5635,51 +5665,51 @@
         <v>150101.205238341</v>
       </c>
       <c r="G72">
-        <f>F72/(E72)</f>
+        <f t="shared" si="17"/>
         <v>1491.9323105849451</v>
       </c>
       <c r="H72">
-        <f>D72/G72</f>
+        <f t="shared" si="18"/>
         <v>50.257005728110236</v>
       </c>
       <c r="I72">
-        <f>C72/G72</f>
+        <f t="shared" si="19"/>
         <v>50.351583665258907</v>
       </c>
-      <c r="J72" s="5">
-        <f>(E72-E71)/E71</f>
+      <c r="J72">
+        <f t="shared" si="20"/>
         <v>3.4588415355902321E-3</v>
       </c>
       <c r="K72" s="4">
-        <f>(E72-E68)/E68</f>
+        <f t="shared" si="21"/>
         <v>2.4067055376474938E-2</v>
       </c>
       <c r="L72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.92704989130222704</v>
       </c>
       <c r="M72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>7.295010869789012E-2</v>
       </c>
       <c r="N72">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000001172</v>
       </c>
       <c r="O72" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2007-3</v>
       </c>
       <c r="P72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.2311361070725771E-2</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.7556943057519877E-3</v>
       </c>
       <c r="R72">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.4067055376475022E-2</v>
       </c>
     </row>
@@ -5703,51 +5733,51 @@
         <v>155203.23635531301</v>
       </c>
       <c r="G73">
-        <f>F73/(E73)</f>
+        <f t="shared" si="17"/>
         <v>1537.6790720828567</v>
       </c>
       <c r="H73">
-        <f>D73/G73</f>
+        <f t="shared" si="18"/>
         <v>50.046731908806372</v>
       </c>
       <c r="I73">
-        <f>C73/G73</f>
+        <f t="shared" si="19"/>
         <v>50.88670678661834</v>
       </c>
-      <c r="J73" s="5">
-        <f>(E73-E72)/E72</f>
+      <c r="J73">
+        <f t="shared" si="20"/>
         <v>3.2288426268046381E-3</v>
       </c>
       <c r="K73" s="4">
-        <f>(E73-E69)/E69</f>
+        <f t="shared" si="21"/>
         <v>2.4938296696785493E-2</v>
       </c>
       <c r="L73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.83755563469252892</v>
       </c>
       <c r="M73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.16244436530742484</v>
       </c>
       <c r="N73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999995381</v>
       </c>
       <c r="O73" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2007-4</v>
       </c>
       <c r="P73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.0887210918026769E-2</v>
       </c>
       <c r="Q73">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>4.0510857787575691E-3</v>
       </c>
       <c r="R73">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.4938296696785489E-2</v>
       </c>
     </row>
@@ -5771,51 +5801,51 @@
         <v>152278.99435676599</v>
       </c>
       <c r="G74">
-        <f>F74/(E74)</f>
+        <f t="shared" si="17"/>
         <v>1494.4800267501319</v>
       </c>
       <c r="H74">
-        <f>D74/G74</f>
+        <f t="shared" si="18"/>
         <v>38.317920863841756</v>
       </c>
       <c r="I74">
-        <f>C74/G74</f>
+        <f t="shared" si="19"/>
         <v>63.576377909698294</v>
       </c>
-      <c r="J74" s="5">
-        <f>(E74-E73)/E73</f>
+      <c r="J74">
+        <f t="shared" si="20"/>
         <v>9.5197398457262453E-3</v>
       </c>
       <c r="K74" s="4">
-        <f>(E74-E70)/E70</f>
+        <f t="shared" si="21"/>
         <v>1.8414164213786909E-2</v>
       </c>
       <c r="L74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.9263496345619999E-2</v>
       </c>
       <c r="M74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.98073650365432596</v>
       </c>
       <c r="N74">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999994593</v>
       </c>
       <c r="O74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2008-1</v>
       </c>
       <c r="P74">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>3.5472118503993071E-4</v>
       </c>
       <c r="Q74">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.8059443028745983E-2</v>
       </c>
       <c r="R74">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.8414164213786943E-2</v>
       </c>
     </row>
@@ -5839,51 +5869,51 @@
         <v>156633.56639887099</v>
       </c>
       <c r="G75">
-        <f>F75/(E75)</f>
+        <f t="shared" si="17"/>
         <v>1536.7810358188235</v>
       </c>
       <c r="H75">
-        <f>D75/G75</f>
+        <f t="shared" si="18"/>
         <v>49.214554301433679</v>
       </c>
       <c r="I75">
-        <f>C75/G75</f>
+        <f t="shared" si="19"/>
         <v>52.708597239419049</v>
       </c>
-      <c r="J75" s="5">
-        <f>(E75-E74)/E74</f>
+      <c r="J75">
+        <f t="shared" si="20"/>
         <v>2.831637065104392E-4</v>
       </c>
       <c r="K75" s="4">
-        <f>(E75-E71)/E71</f>
+        <f t="shared" si="21"/>
         <v>1.6570137674364743E-2</v>
       </c>
       <c r="L75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.63751449824587947</v>
       </c>
       <c r="M75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.36248550175390237</v>
       </c>
       <c r="N75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999978184</v>
       </c>
       <c r="O75" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2008-2</v>
       </c>
       <c r="P75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.0563703005337783E-2</v>
       </c>
       <c r="Q75">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>6.0064346690233451E-3</v>
       </c>
       <c r="R75">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.6570137674364771E-2</v>
       </c>
     </row>
@@ -5907,51 +5937,51 @@
         <v>156659.61218394901</v>
       </c>
       <c r="G76">
-        <f>F76/(E76)</f>
+        <f t="shared" si="17"/>
         <v>1540.5463277366664</v>
       </c>
       <c r="H76">
-        <f>D76/G76</f>
+        <f t="shared" si="18"/>
         <v>51.58195793821411</v>
       </c>
       <c r="I76">
-        <f>C76/G76</f>
+        <f t="shared" si="19"/>
         <v>50.108987256604969</v>
       </c>
-      <c r="J76" s="5">
-        <f>(E76-E75)/E75</f>
+      <c r="J76">
+        <f t="shared" si="20"/>
         <v>-2.278249274316556E-3</v>
       </c>
       <c r="K76" s="4">
-        <f>(E76-E72)/E72</f>
+        <f t="shared" si="21"/>
         <v>1.0758085447536642E-2</v>
       </c>
       <c r="L76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.2241373939409608</v>
       </c>
       <c r="M76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.22413739394101326</v>
       </c>
       <c r="N76">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999994749</v>
       </c>
       <c r="O76" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2008-3</v>
       </c>
       <c r="P76">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.3169374683541679E-2</v>
       </c>
       <c r="Q76">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-2.4112892360056023E-3</v>
       </c>
       <c r="R76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.0758085447536647E-2</v>
       </c>
     </row>
@@ -5975,51 +6005,51 @@
         <v>156889.67045506899</v>
       </c>
       <c r="G77">
-        <f>F77/(E77)</f>
+        <f t="shared" si="17"/>
         <v>1540.9747932797798</v>
       </c>
       <c r="H77">
-        <f>D77/G77</f>
+        <f t="shared" si="18"/>
         <v>48.168966820459147</v>
       </c>
       <c r="I77">
-        <f>C77/G77</f>
+        <f t="shared" si="19"/>
         <v>53.642997359142186</v>
       </c>
-      <c r="J77" s="5">
-        <f>(E77-E76)/E76</f>
+      <c r="J77">
+        <f t="shared" si="20"/>
         <v>1.1900664759302241E-3</v>
       </c>
       <c r="K77" s="4">
-        <f>(E77-E73)/E73</f>
+        <f t="shared" si="21"/>
         <v>8.7040082606026394E-3</v>
       </c>
       <c r="L77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-2.1374053708964706</v>
       </c>
       <c r="M77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>3.1374053708971665</v>
       </c>
       <c r="N77">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000006959</v>
       </c>
       <c r="O77" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2008-4</v>
       </c>
       <c r="P77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.8603994004539329E-2</v>
       </c>
       <c r="Q77">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>2.7308002265148026E-2</v>
       </c>
       <c r="R77">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>8.7040082606026914E-3</v>
       </c>
     </row>
@@ -6043,51 +6073,51 @@
         <v>149995.820481392</v>
       </c>
       <c r="G78">
-        <f>F78/(E78)</f>
+        <f t="shared" si="17"/>
         <v>1463.4241919662065</v>
       </c>
       <c r="H78">
-        <f>D78/G78</f>
+        <f t="shared" si="18"/>
         <v>37.793056471628262</v>
       </c>
       <c r="I78">
-        <f>C78/G78</f>
+        <f t="shared" si="19"/>
         <v>64.703418101381743</v>
       </c>
-      <c r="J78" s="5">
-        <f>(E78-E77)/E77</f>
+      <c r="J78">
+        <f t="shared" si="20"/>
         <v>6.7232804997405917E-3</v>
       </c>
       <c r="K78" s="4">
-        <f>(E78-E74)/E74</f>
+        <f t="shared" si="21"/>
         <v>5.9098085635619236E-3</v>
       </c>
       <c r="L78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.87161322769105998</v>
       </c>
       <c r="M78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.8716132276909774</v>
       </c>
       <c r="N78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.9999999999999174</v>
       </c>
       <c r="O78" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2009-1</v>
       </c>
       <c r="P78">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-5.1510673171224746E-3</v>
       </c>
       <c r="Q78">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.1060875880683911E-2</v>
       </c>
       <c r="R78">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>5.9098085635618247E-3</v>
       </c>
     </row>
@@ -6111,51 +6141,51 @@
         <v>151707.932561897</v>
       </c>
       <c r="G79">
-        <f>F79/(E79)</f>
+        <f t="shared" si="17"/>
         <v>1485.8504889944688</v>
       </c>
       <c r="H79">
-        <f>D79/G79</f>
+        <f t="shared" si="18"/>
         <v>45.614058441866092</v>
       </c>
       <c r="I79">
-        <f>C79/G79</f>
+        <f t="shared" si="19"/>
         <v>56.48768980641379</v>
       </c>
-      <c r="J79" s="5">
-        <f>(E79-E78)/E78</f>
+      <c r="J79">
+        <f t="shared" si="20"/>
         <v>-3.8511209909842421E-3</v>
       </c>
       <c r="K79" s="4">
-        <f>(E79-E75)/E75</f>
+        <f t="shared" si="21"/>
         <v>1.7522682994689318E-3</v>
       </c>
       <c r="L79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-20.1599229428077</v>
       </c>
       <c r="M79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>21.159922942808539</v>
       </c>
       <c r="N79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000008384</v>
       </c>
       <c r="O79" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2009-2</v>
       </c>
       <c r="P79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.532559389241835E-2</v>
       </c>
       <c r="Q79">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.7077862191888751E-2</v>
       </c>
       <c r="R79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.7522682994688399E-3</v>
       </c>
     </row>
@@ -6179,51 +6209,51 @@
         <v>153572.466931078</v>
       </c>
       <c r="G80">
-        <f>F80/(E80)</f>
+        <f t="shared" si="17"/>
         <v>1501.114707069386</v>
       </c>
       <c r="H80">
-        <f>D80/G80</f>
+        <f t="shared" si="18"/>
         <v>48.767682891201247</v>
       </c>
       <c r="I80">
-        <f>C80/G80</f>
+        <f t="shared" si="19"/>
         <v>53.537934532863531</v>
       </c>
-      <c r="J80" s="5">
-        <f>(E80-E79)/E79</f>
+      <c r="J80">
+        <f t="shared" si="20"/>
         <v>1.9967256122711504E-3</v>
       </c>
       <c r="K80" s="4">
-        <f>(E80-E76)/E76</f>
+        <f t="shared" si="21"/>
         <v>6.044512892159919E-3</v>
       </c>
       <c r="L80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-4.5784971454867884</v>
       </c>
       <c r="M80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>5.5784971454862804</v>
       </c>
       <c r="N80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999949196</v>
       </c>
       <c r="O80" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2009-3</v>
       </c>
       <c r="P80">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-2.767478502261228E-2</v>
       </c>
       <c r="Q80">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.3719297914769131E-2</v>
       </c>
       <c r="R80">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>6.0445128921600144E-3</v>
       </c>
     </row>
@@ -6247,51 +6277,51 @@
         <v>158041.74536334901</v>
       </c>
       <c r="G81">
-        <f>F81/(E81)</f>
+        <f t="shared" si="17"/>
         <v>1544.115992683415</v>
       </c>
       <c r="H81">
-        <f>D81/G81</f>
+        <f t="shared" si="18"/>
         <v>47.530944193816488</v>
       </c>
       <c r="I81">
-        <f>C81/G81</f>
+        <f t="shared" si="19"/>
         <v>54.820010081774335</v>
       </c>
-      <c r="J81" s="5">
-        <f>(E81-E80)/E80</f>
+      <c r="J81">
+        <f t="shared" si="20"/>
         <v>4.431511452402786E-4</v>
       </c>
       <c r="K81" s="4">
-        <f>(E81-E77)/E77</f>
+        <f t="shared" si="21"/>
         <v>5.2939760109055965E-3</v>
       </c>
       <c r="L81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-1.1837371992351247</v>
       </c>
       <c r="M81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>2.1837371992342018</v>
       </c>
       <c r="N81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999907718</v>
       </c>
       <c r="O81" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2009-4</v>
       </c>
       <c r="P81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-6.2666763359673283E-3</v>
       </c>
       <c r="Q81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.1560652346868039E-2</v>
       </c>
       <c r="R81">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>5.2939760109056433E-3</v>
       </c>
     </row>
@@ -6315,51 +6345,51 @@
         <v>155143.31367032399</v>
       </c>
       <c r="G82">
-        <f>F82/(E82)</f>
+        <f t="shared" si="17"/>
         <v>1509.3470655996241</v>
       </c>
       <c r="H82">
-        <f>D82/G82</f>
+        <f t="shared" si="18"/>
         <v>40.774429395831376</v>
       </c>
       <c r="I82">
-        <f>C82/G82</f>
+        <f t="shared" si="19"/>
         <v>62.013933338149933</v>
       </c>
-      <c r="J82" s="5">
-        <f>(E82-E81)/E81</f>
+      <c r="J82">
+        <f t="shared" si="20"/>
         <v>4.2736138757655398E-3</v>
       </c>
       <c r="K82" s="4">
-        <f>(E82-E78)/E78</f>
+        <f t="shared" si="21"/>
         <v>2.8477873232906317E-3</v>
       </c>
       <c r="L82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>10.214093350978146</v>
       </c>
       <c r="M82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-9.2140933509770999</v>
       </c>
       <c r="N82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000010463</v>
       </c>
       <c r="O82" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2010-1</v>
       </c>
       <c r="P82">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.9087565563822693E-2</v>
       </c>
       <c r="Q82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-2.6239778240529081E-2</v>
       </c>
       <c r="R82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.847787323290607E-3</v>
       </c>
     </row>
@@ -6383,51 +6413,51 @@
         <v>158410.55206158699</v>
       </c>
       <c r="G83">
-        <f>F83/(E83)</f>
+        <f t="shared" si="17"/>
         <v>1540.6534177320937</v>
       </c>
       <c r="H83">
-        <f>D83/G83</f>
+        <f t="shared" si="18"/>
         <v>48.037973690582035</v>
       </c>
       <c r="I83">
-        <f>C83/G83</f>
+        <f t="shared" si="19"/>
         <v>54.782394757225113</v>
       </c>
-      <c r="J83" s="5">
-        <f>(E83-E82)/E82</f>
+      <c r="J83">
+        <f t="shared" si="20"/>
         <v>3.113748772205577E-4</v>
       </c>
       <c r="K83" s="4">
-        <f>(E83-E79)/E79</f>
+        <f t="shared" si="21"/>
         <v>7.0382751701717431E-3</v>
       </c>
       <c r="L83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>3.3730129633308299</v>
       </c>
       <c r="M83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-2.3730129633304542</v>
       </c>
       <c r="N83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000003757</v>
       </c>
       <c r="O83" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2010-2</v>
       </c>
       <c r="P83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.3740193388478794E-2</v>
       </c>
       <c r="Q83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-1.6701918218304405E-2</v>
       </c>
       <c r="R83">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>7.0382751701716373E-3</v>
       </c>
     </row>
@@ -6451,51 +6481,51 @@
         <v>158633.93463064599</v>
       </c>
       <c r="G84">
-        <f>F84/(E84)</f>
+        <f t="shared" si="17"/>
         <v>1545.6149358354719</v>
       </c>
       <c r="H84">
-        <f>D84/G84</f>
+        <f t="shared" si="18"/>
         <v>48.728575066093896</v>
       </c>
       <c r="I84">
-        <f>C84/G84</f>
+        <f t="shared" si="19"/>
         <v>53.906260398211231</v>
       </c>
-      <c r="J84" s="5">
-        <f>(E84-E83)/E83</f>
+      <c r="J84">
+        <f t="shared" si="20"/>
         <v>-1.8044380340474964E-3</v>
       </c>
       <c r="K84" s="4">
-        <f>(E84-E80)/E80</f>
+        <f t="shared" si="21"/>
         <v>3.2179859574607552E-3</v>
       </c>
       <c r="L84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.11879004285075644</v>
       </c>
       <c r="M84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.1187900428518356</v>
       </c>
       <c r="N84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000010791</v>
       </c>
       <c r="O84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2010-3</v>
       </c>
       <c r="P84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.8226468977989558E-4</v>
       </c>
       <c r="Q84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.6002506472441235E-3</v>
       </c>
       <c r="R84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>3.2179859574608116E-3</v>
       </c>
     </row>
@@ -6519,51 +6549,51 @@
         <v>163984.21962084901</v>
       </c>
       <c r="G85">
-        <f>F85/(E85)</f>
+        <f t="shared" si="17"/>
         <v>1594.3486500805827</v>
       </c>
       <c r="H85">
-        <f>D85/G85</f>
+        <f t="shared" si="18"/>
         <v>49.355012890876644</v>
       </c>
       <c r="I85">
-        <f>C85/G85</f>
+        <f t="shared" si="19"/>
         <v>53.498412307282074</v>
       </c>
-      <c r="J85" s="5">
-        <f>(E85-E84)/E84</f>
+      <c r="J85">
+        <f t="shared" si="20"/>
         <v>2.1297811105277756E-3</v>
       </c>
       <c r="K85" s="4">
-        <f>(E85-E81)/E81</f>
+        <f t="shared" si="21"/>
         <v>4.90929396920962E-3</v>
       </c>
       <c r="L85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>3.6301975201625161</v>
       </c>
       <c r="M85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-2.6301975201627426</v>
       </c>
       <c r="N85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999977351</v>
       </c>
       <c r="O85" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2010-4</v>
       </c>
       <c r="P85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.7821706792773558E-2</v>
       </c>
       <c r="Q85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-1.2912412823565049E-2</v>
       </c>
       <c r="R85">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>4.9092939692096937E-3</v>
       </c>
     </row>
@@ -6587,51 +6617,51 @@
         <v>159594.45750254299</v>
       </c>
       <c r="G86">
-        <f>F86/(E86)</f>
+        <f t="shared" si="17"/>
         <v>1544.0232905010259</v>
       </c>
       <c r="H86">
-        <f>D86/G86</f>
+        <f t="shared" si="18"/>
         <v>41.029584443326435</v>
       </c>
       <c r="I86">
-        <f>C86/G86</f>
+        <f t="shared" si="19"/>
         <v>62.333142326653622</v>
       </c>
-      <c r="J86" s="5">
-        <f>(E86-E85)/E85</f>
+      <c r="J86">
+        <f t="shared" si="20"/>
         <v>4.9517220339504496E-3</v>
       </c>
       <c r="K86" s="4">
-        <f>(E86-E82)/E82</f>
+        <f t="shared" si="21"/>
         <v>5.5878313529077808E-3</v>
       </c>
       <c r="L86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.44423924811250626</v>
       </c>
       <c r="M86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.55576075188706076</v>
       </c>
       <c r="N86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999956701</v>
       </c>
       <c r="O86" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2011-1</v>
       </c>
       <c r="P86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.4823339987952412E-3</v>
       </c>
       <c r="Q86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.1054973541101202E-3</v>
       </c>
       <c r="R86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>5.5878313529078572E-3</v>
       </c>
     </row>
@@ -6655,51 +6685,51 @@
         <v>161873.23598254501</v>
       </c>
       <c r="G87">
-        <f>F87/(E87)</f>
+        <f t="shared" si="17"/>
         <v>1572.4427159938984</v>
       </c>
       <c r="H87">
-        <f>D87/G87</f>
+        <f t="shared" si="18"/>
         <v>46.126801761819394</v>
       </c>
       <c r="I87">
-        <f>C87/G87</f>
+        <f t="shared" si="19"/>
         <v>56.81700301788576</v>
       </c>
-      <c r="J87" s="5">
-        <f>(E87-E86)/E86</f>
+      <c r="J87">
+        <f t="shared" si="20"/>
         <v>-4.0529309100682939E-3</v>
       </c>
       <c r="K87" s="4">
-        <f>(E87-E83)/E83</f>
+        <f t="shared" si="21"/>
         <v>1.2005046642160574E-3</v>
       </c>
       <c r="L87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-15.483058345753687</v>
       </c>
       <c r="M87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>16.483058345753687</v>
       </c>
       <c r="N87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="O87" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2011-2</v>
       </c>
       <c r="P87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.8587483760406656E-2</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.9787988424622711E-2</v>
       </c>
       <c r="R87">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.2005046642160622E-3</v>
       </c>
     </row>
@@ -6723,51 +6753,51 @@
         <v>160149.85257960501</v>
       </c>
       <c r="G88">
-        <f>F88/(E88)</f>
+        <f t="shared" si="17"/>
         <v>1559.0933165957465</v>
       </c>
       <c r="H88">
-        <f>D88/G88</f>
+        <f t="shared" si="18"/>
         <v>48.190597744865556</v>
       </c>
       <c r="I88">
-        <f>C88/G88</f>
+        <f t="shared" si="19"/>
         <v>54.529265700697536</v>
       </c>
-      <c r="J88" s="5">
-        <f>(E88-E87)/E87</f>
+      <c r="J88">
+        <f t="shared" si="20"/>
         <v>-2.1753745611134316E-3</v>
       </c>
       <c r="K88" s="4">
-        <f>(E88-E84)/E84</f>
+        <f t="shared" si="21"/>
         <v>8.2845147920152255E-4</v>
       </c>
       <c r="L88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-6.327062142001286</v>
       </c>
       <c r="M88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>7.3270621420007851</v>
       </c>
       <c r="N88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999949907</v>
       </c>
       <c r="O88" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2011-3</v>
       </c>
       <c r="P88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-5.241663990540919E-3</v>
       </c>
       <c r="Q88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>6.0701154697420266E-3</v>
       </c>
       <c r="R88">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>8.2845147920163065E-4</v>
       </c>
     </row>
@@ -6791,51 +6821,51 @@
         <v>164194.71197013301</v>
       </c>
       <c r="G89">
-        <f>F89/(E89)</f>
+        <f t="shared" si="17"/>
         <v>1601.5384323455824</v>
       </c>
       <c r="H89">
-        <f>D89/G89</f>
+        <f t="shared" si="18"/>
         <v>46.854248475083089</v>
       </c>
       <c r="I89">
-        <f>C89/G89</f>
+        <f t="shared" si="19"/>
         <v>55.6688684567142</v>
       </c>
-      <c r="J89" s="5">
-        <f>(E89-E88)/E88</f>
+      <c r="J89">
+        <f t="shared" si="20"/>
         <v>-1.9153696974126952E-3</v>
       </c>
       <c r="K89" s="4">
-        <f>(E89-E85)/E85</f>
+        <f t="shared" si="21"/>
         <v>-3.2114464416291345E-3</v>
       </c>
       <c r="L89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>7.5710016080944271</v>
       </c>
       <c r="M89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-6.5710016080961475</v>
       </c>
       <c r="N89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.9999999999982796</v>
       </c>
       <c r="O89" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2011-4</v>
       </c>
       <c r="P89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-2.4313866173883304E-2</v>
       </c>
       <c r="Q89">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>2.1102419732259695E-2</v>
       </c>
       <c r="R89">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-3.2114464416291844E-3</v>
       </c>
     </row>
@@ -6859,51 +6889,51 @@
         <v>161049.09992459501</v>
       </c>
       <c r="G90">
-        <f>F90/(E90)</f>
+        <f t="shared" si="17"/>
         <v>1557.3081833784731</v>
       </c>
       <c r="H90">
-        <f>D90/G90</f>
+        <f t="shared" si="18"/>
         <v>39.643933445242979</v>
       </c>
       <c r="I90">
-        <f>C90/G90</f>
+        <f t="shared" si="19"/>
         <v>63.771114162873985</v>
       </c>
-      <c r="J90" s="5">
-        <f>(E90-E89)/E89</f>
+      <c r="J90">
+        <f t="shared" si="20"/>
         <v>8.6998006207063879E-3</v>
       </c>
       <c r="K90" s="4">
-        <f>(E90-E86)/E86</f>
+        <f t="shared" si="21"/>
         <v>5.0618670551754981E-4</v>
       </c>
       <c r="L90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-26.483730907654881</v>
       </c>
       <c r="M90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>27.483730907652976</v>
       </c>
       <c r="N90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999809575</v>
       </c>
       <c r="O90" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2012-1</v>
       </c>
       <c r="P90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.3405712497959132E-2</v>
       </c>
       <c r="Q90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.3911899203475719E-2</v>
       </c>
       <c r="R90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>5.0618670551760836E-4</v>
       </c>
     </row>
@@ -6927,51 +6957,51 @@
         <v>162852.00941157801</v>
       </c>
       <c r="G91">
-        <f>F91/(E91)</f>
+        <f t="shared" si="17"/>
         <v>1579.0863512452747</v>
       </c>
       <c r="H91">
-        <f>D91/G91</f>
+        <f t="shared" si="18"/>
         <v>45.558583536467907</v>
       </c>
       <c r="I91">
-        <f>C91/G91</f>
+        <f t="shared" si="19"/>
         <v>57.571944621889052</v>
       </c>
-      <c r="J91" s="5">
-        <f>(E91-E90)/E90</f>
+      <c r="J91">
+        <f t="shared" si="20"/>
         <v>-2.7512383965453018E-3</v>
       </c>
       <c r="K91" s="4">
-        <f>(E91-E87)/E87</f>
+        <f t="shared" si="21"/>
         <v>1.8138379385876579E-3</v>
       </c>
       <c r="L91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-3.0431016697192228</v>
       </c>
       <c r="M91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>4.0431016697182338</v>
       </c>
       <c r="N91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999901101</v>
       </c>
       <c r="O91" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2012-2</v>
       </c>
       <c r="P91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-5.519693259516175E-3</v>
       </c>
       <c r="Q91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>7.333531198102039E-3</v>
       </c>
       <c r="R91">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.8138379385876924E-3</v>
       </c>
     </row>
@@ -6995,51 +7025,51 @@
         <v>163082.65734558701</v>
       </c>
       <c r="G92">
-        <f>F92/(E92)</f>
+        <f t="shared" si="17"/>
         <v>1584.1112713867503</v>
       </c>
       <c r="H92">
-        <f>D92/G92</f>
+        <f t="shared" si="18"/>
         <v>47.83534291896941</v>
       </c>
       <c r="I92">
-        <f>C92/G92</f>
+        <f t="shared" si="19"/>
         <v>55.113648285936648</v>
       </c>
-      <c r="J92" s="5">
-        <f>(E92-E91)/E91</f>
+      <c r="J92">
+        <f t="shared" si="20"/>
         <v>-1.7602639751078464E-3</v>
       </c>
       <c r="K92" s="4">
-        <f>(E92-E88)/E88</f>
+        <f t="shared" si="21"/>
         <v>2.2306080991279197E-3</v>
       </c>
       <c r="L92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-1.5504661107620623</v>
       </c>
       <c r="M92">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>2.5504661107619695</v>
       </c>
       <c r="N92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999990719</v>
       </c>
       <c r="O92" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2012-3</v>
       </c>
       <c r="P92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.4584822640892224E-3</v>
       </c>
       <c r="Q92">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.6890903632169348E-3</v>
       </c>
       <c r="R92">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.2306080991278954E-3</v>
       </c>
     </row>
@@ -7063,51 +7093,51 @@
         <v>167409.85727373799</v>
       </c>
       <c r="G93">
-        <f>F93/(E93)</f>
+        <f t="shared" si="17"/>
         <v>1627.1550581858228</v>
       </c>
       <c r="H93">
-        <f>D93/G93</f>
+        <f t="shared" si="18"/>
         <v>46.681669506744996</v>
       </c>
       <c r="I93">
-        <f>C93/G93</f>
+        <f t="shared" si="19"/>
         <v>56.20333609339125</v>
       </c>
-      <c r="J93" s="5">
-        <f>(E93-E92)/E92</f>
+      <c r="J93">
+        <f t="shared" si="20"/>
         <v>-6.2152726336717396E-4</v>
       </c>
       <c r="K93" s="4">
-        <f>(E93-E89)/E89</f>
+        <f t="shared" si="21"/>
         <v>3.5298250694010438E-3</v>
       </c>
       <c r="L93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.47688414542019886</v>
       </c>
       <c r="M93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.4768841454201007</v>
       </c>
       <c r="N93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999990186</v>
       </c>
       <c r="O93" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2012-4</v>
       </c>
       <c r="P93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.6833176117041109E-3</v>
       </c>
       <c r="Q93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.2131426811048084E-3</v>
       </c>
       <c r="R93">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>3.5298250694011379E-3</v>
       </c>
     </row>
@@ -7131,51 +7161,51 @@
         <v>162562.98520024499</v>
       </c>
       <c r="G94">
-        <f>F94/(E94)</f>
+        <f t="shared" si="17"/>
         <v>1574.9336175221613</v>
       </c>
       <c r="H94">
-        <f>D94/G94</f>
+        <f t="shared" si="18"/>
         <v>38.695694658211941</v>
       </c>
       <c r="I94">
-        <f>C94/G94</f>
+        <f t="shared" si="19"/>
         <v>64.523249551008504</v>
       </c>
-      <c r="J94" s="5">
-        <f>(E94-E93)/E93</f>
+      <c r="J94">
+        <f t="shared" si="20"/>
         <v>3.245746133132926E-3</v>
       </c>
       <c r="K94" s="4">
-        <f>(E94-E90)/E90</f>
+        <f t="shared" si="21"/>
         <v>-1.8962752851995651E-3</v>
       </c>
       <c r="L94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>4.8354021009551298</v>
       </c>
       <c r="M94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-3.8354021009576296</v>
       </c>
       <c r="N94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999750022</v>
       </c>
       <c r="O94" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2013-1</v>
       </c>
       <c r="P94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-9.1692534980432651E-3</v>
       </c>
       <c r="Q94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>7.2729782128484405E-3</v>
       </c>
       <c r="R94">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.8962752851995335E-3</v>
       </c>
     </row>
@@ -7199,51 +7229,51 @@
         <v>166526.41382985801</v>
       </c>
       <c r="G95">
-        <f>F95/(E95)</f>
+        <f t="shared" si="17"/>
         <v>1612.195158758225</v>
       </c>
       <c r="H95">
-        <f>D95/G95</f>
+        <f t="shared" si="18"/>
         <v>46.021310900510471</v>
       </c>
       <c r="I95">
-        <f>C95/G95</f>
+        <f t="shared" si="19"/>
         <v>57.27041090203047</v>
       </c>
-      <c r="J95" s="5">
-        <f>(E95-E94)/E94</f>
+      <c r="J95">
+        <f t="shared" si="20"/>
         <v>7.0507980757379251E-4</v>
       </c>
       <c r="K95" s="4">
-        <f>(E95-E91)/E91</f>
+        <f t="shared" si="21"/>
         <v>1.5630060958913845E-3</v>
       </c>
       <c r="L95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.8706303302774105</v>
       </c>
       <c r="M95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.8706303302775871</v>
       </c>
       <c r="N95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999982347</v>
       </c>
       <c r="O95" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2013-2</v>
       </c>
       <c r="P95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>4.486812705274291E-3</v>
       </c>
       <c r="Q95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-2.9238066093831825E-3</v>
       </c>
       <c r="R95">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.5630060958913283E-3</v>
       </c>
     </row>
@@ -7267,51 +7297,51 @@
         <v>166468.15152563399</v>
       </c>
       <c r="G96">
-        <f>F96/(E96)</f>
+        <f t="shared" si="17"/>
         <v>1616.5475801209641</v>
       </c>
       <c r="H96">
-        <f>D96/G96</f>
+        <f t="shared" si="18"/>
         <v>47.518606540303971</v>
       </c>
       <c r="I96">
-        <f>C96/G96</f>
+        <f t="shared" si="19"/>
         <v>55.458969605754852</v>
       </c>
-      <c r="J96" s="5">
-        <f>(E96-E95)/E95</f>
+      <c r="J96">
+        <f t="shared" si="20"/>
         <v>-3.0413439818783587E-3</v>
       </c>
       <c r="K96" s="4">
-        <f>(E96-E92)/E92</f>
+        <f t="shared" si="21"/>
         <v>2.7766120695738565E-4</v>
       </c>
       <c r="L96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-11.08053282216407</v>
       </c>
       <c r="M96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>12.080532822155867</v>
       </c>
       <c r="N96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999179678</v>
       </c>
       <c r="O96" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2013-3</v>
       </c>
       <c r="P96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.0766341171330025E-3</v>
       </c>
       <c r="Q96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.3542953240881103E-3</v>
       </c>
       <c r="R96">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.776612069574913E-4</v>
       </c>
     </row>
@@ -7335,51 +7365,51 @@
         <v>170652.893581574</v>
       </c>
       <c r="G97">
-        <f>F97/(E97)</f>
+        <f t="shared" si="17"/>
         <v>1660.5354264223311</v>
       </c>
       <c r="H97">
-        <f>D97/G97</f>
+        <f t="shared" si="18"/>
         <v>46.314424856034471</v>
       </c>
       <c r="I97">
-        <f>C97/G97</f>
+        <f t="shared" si="19"/>
         <v>56.455375092919425</v>
       </c>
-      <c r="J97" s="5">
-        <f>(E97-E96)/E96</f>
+      <c r="J97">
+        <f t="shared" si="20"/>
         <v>-2.0176838966406638E-3</v>
       </c>
       <c r="K97" s="4">
-        <f>(E97-E93)/E93</f>
+        <f t="shared" si="21"/>
         <v>-1.1197516150190374E-3</v>
       </c>
       <c r="L97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>3.1877312175456898</v>
       </c>
       <c r="M97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-2.187731217542606</v>
       </c>
       <c r="N97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000030838</v>
       </c>
       <c r="O97" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2013-4</v>
       </c>
       <c r="P97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.5694671790933888E-3</v>
       </c>
       <c r="Q97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>2.4497155640708984E-3</v>
       </c>
       <c r="R97">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.1197516150189823E-3</v>
       </c>
     </row>
@@ -7403,51 +7433,51 @@
         <v>166468.75723177099</v>
       </c>
       <c r="G98">
-        <f>F98/(E98)</f>
+        <f t="shared" ref="G98:G129" si="29">F98/(E98)</f>
         <v>1614.1839235179739</v>
       </c>
       <c r="H98">
-        <f>D98/G98</f>
+        <f t="shared" ref="H98:H129" si="30">D98/G98</f>
         <v>38.508615038841128</v>
       </c>
       <c r="I98">
-        <f>C98/G98</f>
+        <f t="shared" ref="I98:I129" si="31">C98/G98</f>
         <v>64.620126863734384</v>
       </c>
-      <c r="J98" s="5">
-        <f>(E98-E97)/E97</f>
+      <c r="J98">
+        <f t="shared" si="20"/>
         <v>3.4926793065597683E-3</v>
       </c>
       <c r="K98" s="4">
-        <f>(E98-E94)/E94</f>
+        <f t="shared" si="21"/>
         <v>-8.7389294025485458E-4</v>
       </c>
       <c r="L98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.0740003923302019</v>
       </c>
       <c r="M98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.0740003923309107</v>
       </c>
       <c r="N98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999929123</v>
       </c>
       <c r="O98" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2014-1</v>
       </c>
       <c r="P98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.8124543009431621E-3</v>
       </c>
       <c r="Q98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>9.3856136068892694E-4</v>
       </c>
       <c r="R98">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-8.7389294025486119E-4</v>
       </c>
     </row>
@@ -7471,51 +7501,51 @@
         <v>169560.74810188499</v>
       </c>
       <c r="G99">
-        <f>F99/(E99)</f>
+        <f t="shared" si="29"/>
         <v>1649.7394833010264</v>
       </c>
       <c r="H99">
-        <f>D99/G99</f>
+        <f t="shared" si="30"/>
         <v>46.238943746876608</v>
       </c>
       <c r="I99">
-        <f>C99/G99</f>
+        <f t="shared" si="31"/>
         <v>56.541373884004663</v>
       </c>
-      <c r="J99" s="5">
-        <f>(E99-E98)/E98</f>
+      <c r="J99">
+        <f t="shared" ref="J99:J130" si="32">(E99-E98)/E98</f>
         <v>-3.378537013698414E-3</v>
       </c>
       <c r="K99" s="4">
-        <f>(E99-E95)/E95</f>
+        <f t="shared" si="21"/>
         <v>-4.9510663849484157E-3</v>
       </c>
       <c r="L99">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.42555938810531396</v>
       </c>
       <c r="M99">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.4255593881046609</v>
       </c>
       <c r="N99">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999934697</v>
       </c>
       <c r="O99" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2014-2</v>
       </c>
       <c r="P99">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.1069727812474365E-3</v>
       </c>
       <c r="Q99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-7.058039166192619E-3</v>
       </c>
       <c r="R99">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-4.951066384948466E-3</v>
       </c>
     </row>
@@ -7539,51 +7569,51 @@
         <v>169455.62759426501</v>
       </c>
       <c r="G100">
-        <f>F100/(E100)</f>
+        <f t="shared" si="29"/>
         <v>1654.6907151373648</v>
       </c>
       <c r="H100">
-        <f>D100/G100</f>
+        <f t="shared" si="30"/>
         <v>47.579579469942566</v>
       </c>
       <c r="I100">
-        <f>C100/G100</f>
+        <f t="shared" si="31"/>
         <v>54.82966598243064</v>
       </c>
-      <c r="J100" s="5">
-        <f>(E100-E99)/E99</f>
+      <c r="J100">
+        <f t="shared" si="32"/>
         <v>-3.6103427880097359E-3</v>
       </c>
       <c r="K100" s="4">
-        <f>(E100-E96)/E96</f>
+        <f t="shared" si="21"/>
         <v>-5.5189752464157591E-3</v>
       </c>
       <c r="L100">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.1072842454507357</v>
       </c>
       <c r="M100">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.1072842454500731</v>
       </c>
       <c r="N100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999933742</v>
       </c>
       <c r="O100" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2014-3</v>
       </c>
       <c r="P100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>5.9209909497300278E-4</v>
       </c>
       <c r="Q100">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-6.1110743413851053E-3</v>
       </c>
       <c r="R100">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-5.5189752464157582E-3</v>
       </c>
     </row>
@@ -7607,51 +7637,51 @@
         <v>173536.81628387599</v>
       </c>
       <c r="G101">
-        <f>F101/(E101)</f>
+        <f t="shared" si="29"/>
         <v>1710.0099411646765</v>
       </c>
       <c r="H101">
-        <f>D101/G101</f>
+        <f t="shared" si="30"/>
         <v>45.813470878643024</v>
       </c>
       <c r="I101">
-        <f>C101/G101</f>
+        <f t="shared" si="31"/>
         <v>55.6694574402892</v>
       </c>
-      <c r="J101" s="5">
-        <f>(E101-E100)/E100</f>
+      <c r="J101">
+        <f t="shared" si="32"/>
         <v>-9.0452490822403465E-3</v>
       </c>
       <c r="K101" s="4">
-        <f>(E101-E97)/E97</f>
+        <f t="shared" si="21"/>
         <v>-1.2521885132219756E-2</v>
       </c>
       <c r="L101">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.38928045789841559</v>
       </c>
       <c r="M101">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.61071954210132484</v>
       </c>
       <c r="N101">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999974043</v>
       </c>
       <c r="O101" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2014-4</v>
       </c>
       <c r="P101">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-4.8745251780218692E-3</v>
       </c>
       <c r="Q101">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-7.6473599541946368E-3</v>
       </c>
       <c r="R101">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.2521885132219746E-2</v>
       </c>
     </row>
@@ -7675,51 +7705,51 @@
         <v>167337.95286155201</v>
       </c>
       <c r="G102">
-        <f>F102/(E102)</f>
+        <f t="shared" si="29"/>
         <v>1644.1087795494916</v>
       </c>
       <c r="H102">
-        <f>D102/G102</f>
+        <f t="shared" si="30"/>
         <v>37.657462066480264</v>
       </c>
       <c r="I102">
-        <f>C102/G102</f>
+        <f t="shared" si="31"/>
         <v>64.122879321517829</v>
       </c>
-      <c r="J102" s="5">
-        <f>(E102-E101)/E101</f>
+      <c r="J102">
+        <f t="shared" si="32"/>
         <v>2.9306709413363169E-3</v>
       </c>
       <c r="K102" s="4">
-        <f>(E102-E98)/E98</f>
+        <f t="shared" ref="K102:K133" si="33">(E102-E98)/E98</f>
         <v>-1.3074924504080722E-2</v>
       </c>
       <c r="L102">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.63123156892882026</v>
       </c>
       <c r="M102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.36876843107149587</v>
       </c>
       <c r="N102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000003162</v>
       </c>
       <c r="O102" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2015-1</v>
       </c>
       <c r="P102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-8.2533051083367517E-3</v>
       </c>
       <c r="Q102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-4.8216193957481036E-3</v>
       </c>
       <c r="R102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.3074924504080765E-2</v>
       </c>
     </row>
@@ -7743,51 +7773,51 @@
         <v>169153.90686676701</v>
       </c>
       <c r="G103">
-        <f>F103/(E103)</f>
+        <f t="shared" si="29"/>
         <v>1670.2505886522727</v>
       </c>
       <c r="H103">
-        <f>D103/G103</f>
+        <f t="shared" si="30"/>
         <v>44.029805903358273</v>
       </c>
       <c r="I103">
-        <f>C103/G103</f>
+        <f t="shared" si="31"/>
         <v>57.244762126135953</v>
       </c>
-      <c r="J103" s="5">
-        <f>(E103-E102)/E102</f>
+      <c r="J103">
+        <f t="shared" si="32"/>
         <v>-4.9692637262429371E-3</v>
       </c>
       <c r="K103" s="4">
-        <f>(E103-E99)/E99</f>
+        <f t="shared" si="33"/>
         <v>-1.4650174625794142E-2</v>
       </c>
       <c r="L103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.4671349349741984</v>
       </c>
       <c r="M103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.46713493497416553</v>
       </c>
       <c r="N103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000329</v>
       </c>
       <c r="O103" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2015-2</v>
       </c>
       <c r="P103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-2.1493782996975141E-2</v>
       </c>
       <c r="Q103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>6.8436083711805162E-3</v>
       </c>
       <c r="R103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.4650174625794099E-2</v>
       </c>
     </row>
@@ -7811,51 +7841,51 @@
         <v>169323.059931945</v>
       </c>
       <c r="G104">
-        <f>F104/(E104)</f>
+        <f t="shared" si="29"/>
         <v>1676.3535623648779</v>
       </c>
       <c r="H104">
-        <f>D104/G104</f>
+        <f t="shared" si="30"/>
         <v>45.528691813484976</v>
       </c>
       <c r="I104">
-        <f>C104/G104</f>
+        <f t="shared" si="31"/>
         <v>55.478078913972077</v>
       </c>
-      <c r="J104" s="5">
-        <f>(E104-E103)/E103</f>
+      <c r="J104">
+        <f t="shared" si="32"/>
         <v>-2.6442700003323663E-3</v>
       </c>
       <c r="K104" s="4">
-        <f>(E104-E100)/E100</f>
+        <f t="shared" si="33"/>
         <v>-1.3694805764077686E-2</v>
       </c>
       <c r="L104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.4623348428474672</v>
       </c>
       <c r="M104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.46233484284736082</v>
       </c>
       <c r="N104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000001064</v>
       </c>
       <c r="O104" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2015-3</v>
       </c>
       <c r="P104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-2.002639163483913E-2</v>
       </c>
       <c r="Q104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>6.3315858707599882E-3</v>
       </c>
       <c r="R104">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.3694805764077667E-2</v>
       </c>
     </row>
@@ -7879,51 +7909,51 @@
         <v>173817.82002561999</v>
       </c>
       <c r="G105">
-        <f>F105/(E105)</f>
+        <f t="shared" si="29"/>
         <v>1734.3246849203408</v>
       </c>
       <c r="H105">
-        <f>D105/G105</f>
+        <f t="shared" si="30"/>
         <v>44.517884085776906</v>
       </c>
       <c r="I105">
-        <f>C105/G105</f>
+        <f t="shared" si="31"/>
         <v>55.704307028111266</v>
       </c>
-      <c r="J105" s="5">
-        <f>(E105-E104)/E104</f>
+      <c r="J105">
+        <f t="shared" si="32"/>
         <v>-7.7675942703484425E-3</v>
       </c>
       <c r="K105" s="4">
-        <f>(E105-E101)/E101</f>
+        <f t="shared" si="33"/>
         <v>-1.242314570468302E-2</v>
       </c>
       <c r="L105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.0276422300243822</v>
       </c>
       <c r="M105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-2.7642230024337168E-2</v>
       </c>
       <c r="N105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000451</v>
       </c>
       <c r="O105" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2015-4</v>
       </c>
       <c r="P105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.2766549155878283E-2</v>
       </c>
       <c r="Q105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>3.4340345119470431E-4</v>
       </c>
       <c r="R105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.2423145704683058E-2</v>
       </c>
     </row>
@@ -7947,51 +7977,51 @@
         <v>168900.67024464501</v>
       </c>
       <c r="G106">
-        <f>F106/(E106)</f>
+        <f t="shared" si="29"/>
         <v>1680.6423800399098</v>
       </c>
       <c r="H106">
-        <f>D106/G106</f>
+        <f t="shared" si="30"/>
         <v>37.748265105007654</v>
       </c>
       <c r="I106">
-        <f>C106/G106</f>
+        <f t="shared" si="31"/>
         <v>62.749420928968057</v>
       </c>
-      <c r="J106" s="5">
-        <f>(E106-E105)/E105</f>
+      <c r="J106">
+        <f t="shared" si="32"/>
         <v>2.7488415192892103E-3</v>
       </c>
       <c r="K106" s="4">
-        <f>(E106-E102)/E102</f>
+        <f t="shared" si="33"/>
         <v>-1.2602191508990784E-2</v>
       </c>
       <c r="L106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-7.0793014072455251E-2</v>
       </c>
       <c r="M106">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.0707930140727433</v>
       </c>
       <c r="N106">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.000000000000288</v>
       </c>
       <c r="O106" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2016-1</v>
       </c>
       <c r="P106">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>8.9214712083976065E-4</v>
       </c>
       <c r="Q106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-1.3494338629834174E-2</v>
       </c>
       <c r="R106">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.2602191508990779E-2</v>
       </c>
     </row>
@@ -8015,51 +8045,51 @@
         <v>172752.52254261501</v>
       </c>
       <c r="G107">
-        <f>F107/(E107)</f>
+        <f t="shared" si="29"/>
         <v>1715.5285429967646</v>
       </c>
       <c r="H107">
-        <f>D107/G107</f>
+        <f t="shared" si="30"/>
         <v>44.085156826426804</v>
       </c>
       <c r="I107">
-        <f>C107/G107</f>
+        <f t="shared" si="31"/>
         <v>56.614142668085279</v>
       </c>
-      <c r="J107" s="5">
-        <f>(E107-E106)/E106</f>
+      <c r="J107">
+        <f t="shared" si="32"/>
         <v>2.0061502756177729E-3</v>
       </c>
       <c r="K107" s="4">
-        <f>(E107-E103)/E103</f>
+        <f t="shared" si="33"/>
         <v>-5.6802862374536797E-3</v>
       </c>
       <c r="L107">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-9.62175396404438E-2</v>
       </c>
       <c r="M107">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.0962175396406908</v>
       </c>
       <c r="N107">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000002469</v>
       </c>
       <c r="O107" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2016-2</v>
       </c>
       <c r="P107">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>5.4654316622126681E-4</v>
       </c>
       <c r="Q107">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-6.2268294036763499E-3</v>
       </c>
       <c r="R107">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-5.6802862374536467E-3</v>
       </c>
     </row>
@@ -8083,51 +8113,51 @@
         <v>171875.29729059199</v>
       </c>
       <c r="G108">
-        <f>F108/(E108)</f>
+        <f t="shared" si="29"/>
         <v>1708.9970177711659</v>
       </c>
       <c r="H108">
-        <f>D108/G108</f>
+        <f t="shared" si="30"/>
         <v>45.127227238113676</v>
       </c>
       <c r="I108">
-        <f>C108/G108</f>
+        <f t="shared" si="31"/>
         <v>55.443631284944402</v>
       </c>
-      <c r="J108" s="5">
-        <f>(E108-E107)/E107</f>
+      <c r="J108">
+        <f t="shared" si="32"/>
         <v>-1.2754902178936951E-3</v>
       </c>
       <c r="K108" s="4">
-        <f>(E108-E104)/E104</f>
+        <f t="shared" si="33"/>
         <v>-4.3156731104214288E-3</v>
       </c>
       <c r="L108">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.92097576374310697</v>
       </c>
       <c r="M108">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>7.9024236256860447E-2</v>
       </c>
       <c r="N108">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999996736</v>
       </c>
       <c r="O108" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2016-3</v>
       </c>
       <c r="P108">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-3.9746303389359651E-3</v>
       </c>
       <c r="Q108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-3.4104277148532279E-4</v>
       </c>
       <c r="R108">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-4.3156731104214696E-3</v>
       </c>
     </row>
@@ -8151,51 +8181,51 @@
         <v>174875.699207117</v>
       </c>
       <c r="G109">
-        <f>F109/(E109)</f>
+        <f t="shared" si="29"/>
         <v>1748.4248926972764</v>
       </c>
       <c r="H109">
-        <f>D109/G109</f>
+        <f t="shared" si="30"/>
         <v>44.025427419416204</v>
       </c>
       <c r="I109">
-        <f>C109/G109</f>
+        <f t="shared" si="31"/>
         <v>55.993566783610859</v>
       </c>
-      <c r="J109" s="5">
-        <f>(E109-E108)/E108</f>
+      <c r="J109">
+        <f t="shared" si="32"/>
         <v>-5.48731837567514E-3</v>
       </c>
       <c r="K109" s="4">
-        <f>(E109-E105)/E105</f>
+        <f t="shared" si="33"/>
         <v>-2.0274642631799159E-3</v>
       </c>
       <c r="L109">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.4235440601633238</v>
       </c>
       <c r="M109">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.423544060162764</v>
       </c>
       <c r="N109">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000005598</v>
       </c>
       <c r="O109" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2016-4</v>
       </c>
       <c r="P109">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-4.9136489722230951E-3</v>
       </c>
       <c r="Q109">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>2.8861847090420442E-3</v>
       </c>
       <c r="R109">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-2.0274642631799011E-3</v>
       </c>
     </row>
@@ -8219,51 +8249,51 @@
         <v>170357.82306401501</v>
       </c>
       <c r="G110">
-        <f>F110/(E110)</f>
+        <f t="shared" si="29"/>
         <v>1698.6556568416822</v>
       </c>
       <c r="H110">
-        <f>D110/G110</f>
+        <f t="shared" si="30"/>
         <v>37.79792652495928</v>
       </c>
       <c r="I110">
-        <f>C110/G110</f>
+        <f t="shared" si="31"/>
         <v>62.491865804559929</v>
       </c>
-      <c r="J110" s="5">
-        <f>(E110-E109)/E109</f>
+      <c r="J110">
+        <f t="shared" si="32"/>
         <v>2.7074670031404994E-3</v>
       </c>
       <c r="K110" s="4">
-        <f>(E110-E106)/E106</f>
+        <f t="shared" si="33"/>
         <v>-2.0686417037175209E-3</v>
       </c>
       <c r="L110">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.2388789024724865</v>
       </c>
       <c r="M110">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.2388789024701281</v>
       </c>
       <c r="N110">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999764166</v>
       </c>
       <c r="O110" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2017-1</v>
       </c>
       <c r="P110">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>4.9415485979285596E-4</v>
       </c>
       <c r="Q110">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-2.5627965635054983E-3</v>
       </c>
       <c r="R110">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-2.0686417037175664E-3</v>
       </c>
     </row>
@@ -8287,51 +8317,51 @@
         <v>172105.55431778901</v>
       </c>
       <c r="G111">
-        <f>F111/(E111)</f>
+        <f t="shared" si="29"/>
         <v>1726.9616315182402</v>
       </c>
       <c r="H111">
-        <f>D111/G111</f>
+        <f t="shared" si="30"/>
         <v>42.528100827889482</v>
       </c>
       <c r="I111">
-        <f>C111/G111</f>
+        <f t="shared" si="31"/>
         <v>57.129906146176609</v>
       </c>
-      <c r="J111" s="5">
-        <f>(E111-E110)/E110</f>
+      <c r="J111">
+        <f t="shared" si="32"/>
         <v>-6.2995978033065112E-3</v>
       </c>
       <c r="K111" s="4">
-        <f>(E111-E107)/E107</f>
+        <f t="shared" si="33"/>
         <v>-1.034061334759191E-2</v>
       </c>
       <c r="L111">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.4953108449009649</v>
       </c>
       <c r="M111">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.49531084490107413</v>
       </c>
       <c r="N111">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999989075</v>
       </c>
       <c r="O111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2017-2</v>
       </c>
       <c r="P111">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.5462431281581854E-2</v>
       </c>
       <c r="Q111">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.1218179339910736E-3</v>
       </c>
       <c r="R111">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.0340613347591954E-2</v>
       </c>
     </row>
@@ -8355,51 +8385,51 @@
         <v>173640.620088089</v>
       </c>
       <c r="G112">
-        <f>F112/(E112)</f>
+        <f t="shared" si="29"/>
         <v>1732.1598134685805</v>
       </c>
       <c r="H112">
-        <f>D112/G112</f>
+        <f t="shared" si="30"/>
         <v>44.627765350968879</v>
       </c>
       <c r="I112">
-        <f>C112/G112</f>
+        <f t="shared" si="31"/>
         <v>55.617384512184309</v>
       </c>
-      <c r="J112" s="5">
-        <f>(E112-E111)/E111</f>
+      <c r="J112">
+        <f t="shared" si="32"/>
         <v>5.8915776756392211E-3</v>
       </c>
       <c r="K112" s="4">
-        <f>(E112-E108)/E108</f>
+        <f t="shared" si="33"/>
         <v>-3.2385987818760488E-3</v>
       </c>
       <c r="L112">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.5334621047241099</v>
       </c>
       <c r="M112">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.53346210472445899</v>
       </c>
       <c r="N112">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999965095</v>
       </c>
       <c r="O112" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2017-3</v>
       </c>
       <c r="P112">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-4.966268504412584E-3</v>
       </c>
       <c r="Q112">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.727669722537666E-3</v>
       </c>
       <c r="R112">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-3.2385987818760453E-3</v>
       </c>
     </row>
@@ -8423,51 +8453,51 @@
         <v>179738.65235853201</v>
       </c>
       <c r="G113">
-        <f>F113/(E113)</f>
+        <f t="shared" si="29"/>
         <v>1793.1604720187829</v>
       </c>
       <c r="H113">
-        <f>D113/G113</f>
+        <f t="shared" si="30"/>
         <v>44.608844485193991</v>
       </c>
       <c r="I113">
-        <f>C113/G113</f>
+        <f t="shared" si="31"/>
         <v>55.626831664959745</v>
       </c>
-      <c r="J113" s="5">
-        <f>(E113-E112)/E112</f>
+      <c r="J113">
+        <f t="shared" si="32"/>
         <v>-9.4505450008597542E-5</v>
       </c>
       <c r="K113" s="4">
-        <f>(E113-E109)/E109</f>
+        <f t="shared" si="33"/>
         <v>2.1664079793400136E-3</v>
       </c>
       <c r="L113">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.6925042603380276</v>
       </c>
       <c r="M113">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.6925042603395362</v>
       </c>
       <c r="N113">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999849143</v>
       </c>
       <c r="O113" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2017-4</v>
       </c>
       <c r="P113">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>5.8330627140032844E-3</v>
       </c>
       <c r="Q113">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-3.6666547346665386E-3</v>
       </c>
       <c r="R113">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.1664079793399793E-3</v>
       </c>
     </row>
@@ -8491,51 +8521,51 @@
         <v>176666.87187394401</v>
       </c>
       <c r="G114">
-        <f>F114/(E114)</f>
+        <f t="shared" si="29"/>
         <v>1759.7889003577009</v>
       </c>
       <c r="H114">
-        <f>D114/G114</f>
+        <f t="shared" si="30"/>
         <v>37.772533943416803</v>
       </c>
       <c r="I114">
-        <f>C114/G114</f>
+        <f t="shared" si="31"/>
         <v>62.618411719459843</v>
       </c>
-      <c r="J114" s="5">
-        <f>(E114-E113)/E113</f>
+      <c r="J114">
+        <f t="shared" si="32"/>
         <v>1.5490443990261516E-3</v>
       </c>
       <c r="K114" s="4">
-        <f>(E114-E110)/E110</f>
+        <f t="shared" si="33"/>
         <v>1.008610457838448E-3</v>
       </c>
       <c r="L114">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-0.25103059582433895</v>
       </c>
       <c r="M114">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.2510305958187897</v>
       </c>
       <c r="N114">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999445077</v>
       </c>
       <c r="O114" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2018-1</v>
       </c>
       <c r="P114">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-2.5319208418584488E-4</v>
       </c>
       <c r="Q114">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.2618025420186958E-3</v>
       </c>
       <c r="R114">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.0086104578383992E-3</v>
       </c>
     </row>
@@ -8559,51 +8589,51 @@
         <v>182224.97170210199</v>
       </c>
       <c r="G115">
-        <f>F115/(E115)</f>
+        <f t="shared" si="29"/>
         <v>1803.7348431001574</v>
       </c>
       <c r="H115">
-        <f>D115/G115</f>
+        <f t="shared" si="30"/>
         <v>45.605489837588721</v>
       </c>
       <c r="I115">
-        <f>C115/G115</f>
+        <f t="shared" si="31"/>
         <v>55.420984424506329</v>
       </c>
-      <c r="J115" s="5">
-        <f>(E115-E114)/E114</f>
+      <c r="J115">
+        <f t="shared" si="32"/>
         <v>6.3305370322156457E-3</v>
       </c>
       <c r="K115" s="4">
-        <f>(E115-E111)/E111</f>
+        <f t="shared" si="33"/>
         <v>1.3731634111298375E-2</v>
       </c>
       <c r="L115">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.248785218776681</v>
       </c>
       <c r="M115">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.2487852187767796</v>
       </c>
       <c r="N115">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999990141</v>
       </c>
       <c r="O115" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2018-2</v>
       </c>
       <c r="P115">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>3.0879495819137452E-2</v>
       </c>
       <c r="Q115">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-1.7147861707840429E-2</v>
       </c>
       <c r="R115">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>1.3731634111298296E-2</v>
       </c>
     </row>
@@ -8627,51 +8657,51 @@
         <v>180280.021769232</v>
       </c>
       <c r="G116">
-        <f>F116/(E116)</f>
+        <f t="shared" si="29"/>
         <v>1783.1921833061999</v>
       </c>
       <c r="H116">
-        <f>D116/G116</f>
+        <f t="shared" si="30"/>
         <v>46.477429492487062</v>
       </c>
       <c r="I116">
-        <f>C116/G116</f>
+        <f t="shared" si="31"/>
         <v>54.622173487477198</v>
       </c>
-      <c r="J116" s="5">
-        <f>(E116-E115)/E115</f>
+      <c r="J116">
+        <f t="shared" si="32"/>
         <v>7.238569731661792E-4</v>
       </c>
       <c r="K116" s="4">
-        <f>(E116-E112)/E112</f>
+        <f t="shared" si="33"/>
         <v>8.5236354873770466E-3</v>
       </c>
       <c r="L116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.1647345010824215</v>
       </c>
       <c r="M116">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.1647345010823382</v>
       </c>
       <c r="N116">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000833</v>
       </c>
       <c r="O116" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2018-3</v>
       </c>
       <c r="P116">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.8451407814175574E-2</v>
       </c>
       <c r="Q116">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-9.9277723267978176E-3</v>
       </c>
       <c r="R116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>8.5236354873770015E-3</v>
       </c>
     </row>
@@ -8695,51 +8725,51 @@
         <v>185211.37954587699</v>
       </c>
       <c r="G117">
-        <f>F117/(E117)</f>
+        <f t="shared" si="29"/>
         <v>1835.5094035485258</v>
       </c>
       <c r="H117">
-        <f>D117/G117</f>
+        <f t="shared" si="30"/>
         <v>45.214967531323502</v>
       </c>
       <c r="I117">
-        <f>C117/G117</f>
+        <f t="shared" si="31"/>
         <v>55.689652836087802</v>
       </c>
-      <c r="J117" s="5">
-        <f>(E117-E116)/E116</f>
+      <c r="J117">
+        <f t="shared" si="32"/>
         <v>-1.9286189738217567E-3</v>
       </c>
       <c r="K117" s="4">
-        <f>(E117-E113)/E113</f>
+        <f t="shared" si="33"/>
         <v>6.6737138207648514E-3</v>
       </c>
       <c r="L117">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.9060890736374404</v>
       </c>
       <c r="M117">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>9.3910926363420022E-2</v>
       </c>
       <c r="N117">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000008604</v>
       </c>
       <c r="O117" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2018-4</v>
       </c>
       <c r="P117">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>6.0469791735782074E-3</v>
       </c>
       <c r="Q117">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>6.2673464719238648E-4</v>
       </c>
       <c r="R117">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>6.6737138207648705E-3</v>
       </c>
     </row>
@@ -8763,51 +8793,51 @@
         <v>180335.30761935201</v>
       </c>
       <c r="G118">
-        <f>F118/(E118)</f>
+        <f t="shared" si="29"/>
         <v>1780.5387651618391</v>
       </c>
       <c r="H118">
-        <f>D118/G118</f>
+        <f t="shared" si="30"/>
         <v>37.687452002646438</v>
       </c>
       <c r="I118">
-        <f>C118/G118</f>
+        <f t="shared" si="31"/>
         <v>63.593863039635657</v>
       </c>
-      <c r="J118" s="5">
-        <f>(E118-E117)/E117</f>
+      <c r="J118">
+        <f t="shared" si="32"/>
         <v>3.7331756811471491E-3</v>
       </c>
       <c r="K118" s="4">
-        <f>(E118-E114)/E114</f>
+        <f t="shared" si="33"/>
         <v>8.8690207421190381E-3</v>
       </c>
       <c r="L118">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-9.5558026520658479E-2</v>
       </c>
       <c r="M118">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>1.0955580265211613</v>
       </c>
       <c r="N118">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000005027</v>
       </c>
       <c r="O118" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2019-1</v>
       </c>
       <c r="P118">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-8.4750611928768123E-4</v>
       </c>
       <c r="Q118">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>9.7165268614111781E-3</v>
       </c>
       <c r="R118">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>8.8690207421189271E-3</v>
       </c>
     </row>
@@ -8831,51 +8861,51 @@
         <v>182717.05128259401</v>
       </c>
       <c r="G119">
-        <f>F119/(E119)</f>
+        <f t="shared" si="29"/>
         <v>1811.1527460794541</v>
       </c>
       <c r="H119">
-        <f>D119/G119</f>
+        <f t="shared" si="30"/>
         <v>44.068831704175153</v>
       </c>
       <c r="I119">
-        <f>C119/G119</f>
+        <f t="shared" si="31"/>
         <v>56.815564533588912</v>
       </c>
-      <c r="J119" s="5">
-        <f>(E119-E118)/E118</f>
+      <c r="J119">
+        <f t="shared" si="32"/>
         <v>-3.9189736463463862E-3</v>
       </c>
       <c r="K119" s="4">
-        <f>(E119-E115)/E115</f>
+        <f t="shared" si="33"/>
         <v>-1.4063444791946643E-3</v>
       </c>
       <c r="L119">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>10.815593337880426</v>
       </c>
       <c r="M119">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-9.8155933378805251</v>
       </c>
       <c r="N119">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999990052</v>
       </c>
       <c r="O119" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2019-2</v>
       </c>
       <c r="P119">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.5210449979942729E-2</v>
       </c>
       <c r="Q119">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.3804105500748204E-2</v>
       </c>
       <c r="R119">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.4063444791946322E-3</v>
       </c>
     </row>
@@ -8899,51 +8929,51 @@
         <v>182267.73681068499</v>
       </c>
       <c r="G120">
-        <f>F120/(E120)</f>
+        <f t="shared" si="29"/>
         <v>1810.8049794678634</v>
       </c>
       <c r="H120">
-        <f>D120/G120</f>
+        <f t="shared" si="30"/>
         <v>45.224350954549266</v>
       </c>
       <c r="I120">
-        <f>C120/G120</f>
+        <f t="shared" si="31"/>
         <v>55.43129052940975</v>
       </c>
-      <c r="J120" s="5">
-        <f>(E120-E119)/E119</f>
+      <c r="J120">
+        <f t="shared" si="32"/>
         <v>-2.2674939072427386E-3</v>
       </c>
       <c r="K120" s="4">
-        <f>(E120-E116)/E116</f>
+        <f t="shared" si="33"/>
         <v>-4.3913277888241245E-3</v>
       </c>
       <c r="L120">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.8224937279778812</v>
       </c>
       <c r="M120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.8224937279773372</v>
       </c>
       <c r="N120">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.000000000000544</v>
       </c>
       <c r="O120" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2019-3</v>
       </c>
       <c r="P120">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.239449514145107E-2</v>
       </c>
       <c r="Q120">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>8.0031673526245566E-3</v>
       </c>
       <c r="R120">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-4.3913277888241176E-3</v>
       </c>
     </row>
@@ -8967,51 +8997,51 @@
         <v>186480.67279025799</v>
       </c>
       <c r="G121">
-        <f>F121/(E121)</f>
+        <f t="shared" si="29"/>
         <v>1859.8337715501875</v>
       </c>
       <c r="H121">
-        <f>D121/G121</f>
+        <f t="shared" si="30"/>
         <v>43.714390096333979</v>
       </c>
       <c r="I121">
-        <f>C121/G121</f>
+        <f t="shared" si="31"/>
         <v>56.552997044843018</v>
       </c>
-      <c r="J121" s="5">
-        <f>(E121-E120)/E120</f>
+      <c r="J121">
+        <f t="shared" si="32"/>
         <v>-3.8572536726009495E-3</v>
       </c>
       <c r="K121" s="4">
-        <f>(E121-E117)/E117</f>
+        <f t="shared" si="33"/>
         <v>-6.3152036439335195E-3</v>
       </c>
       <c r="L121">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.3548323803794986</v>
       </c>
       <c r="M121">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.3548323803790192</v>
       </c>
       <c r="N121">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000004794</v>
       </c>
       <c r="O121" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2019-4</v>
       </c>
       <c r="P121">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.4871246029425253E-2</v>
       </c>
       <c r="Q121">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>8.5560423854887067E-3</v>
       </c>
       <c r="R121">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-6.3152036439335646E-3</v>
       </c>
     </row>
@@ -9035,51 +9065,51 @@
         <v>178413.50497224601</v>
       </c>
       <c r="G122">
-        <f>F122/(E122)</f>
+        <f t="shared" si="29"/>
         <v>1780.6084723451443</v>
       </c>
       <c r="H122">
-        <f>D122/G122</f>
+        <f t="shared" si="30"/>
         <v>35.747265599072492</v>
       </c>
       <c r="I122">
-        <f>C122/G122</f>
+        <f t="shared" si="31"/>
         <v>64.450789022821283</v>
       </c>
-      <c r="J122" s="5">
-        <f>(E122-E121)/E121</f>
+      <c r="J122">
+        <f t="shared" si="32"/>
         <v>-6.9147627418847575E-4</v>
       </c>
       <c r="K122" s="4">
-        <f>(E122-E118)/E118</f>
+        <f t="shared" si="33"/>
         <v>-1.06955603798763E-2</v>
       </c>
       <c r="L122">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.7910618416936277</v>
       </c>
       <c r="M122">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.7910618416933326</v>
       </c>
       <c r="N122">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000002951</v>
       </c>
       <c r="O122" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2020-1</v>
       </c>
       <c r="P122">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.9156410071926644E-2</v>
       </c>
       <c r="Q122">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>8.4608496920471864E-3</v>
       </c>
       <c r="R122">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.069556037987629E-2</v>
       </c>
     </row>
@@ -9103,51 +9133,51 @@
         <v>168021.05899440401</v>
       </c>
       <c r="G123">
-        <f>F123/(E123)</f>
+        <f t="shared" si="29"/>
         <v>1685.1074941628333</v>
       </c>
       <c r="H123">
-        <f>D123/G123</f>
+        <f t="shared" si="30"/>
         <v>42.368443766161725</v>
       </c>
       <c r="I123">
-        <f>C123/G123</f>
+        <f t="shared" si="31"/>
         <v>57.340957311469467</v>
       </c>
-      <c r="J123" s="5">
-        <f>(E123-E122)/E122</f>
+      <c r="J123">
+        <f t="shared" si="32"/>
         <v>-4.8768765631905658E-3</v>
       </c>
       <c r="K123" s="4">
-        <f>(E123-E119)/E119</f>
+        <f t="shared" si="33"/>
         <v>-1.1646946445152634E-2</v>
       </c>
       <c r="L123">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.4471446314904433</v>
       </c>
       <c r="M123">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.44714463149037664</v>
       </c>
       <c r="N123">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000666</v>
       </c>
       <c r="O123" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2020-2</v>
       </c>
       <c r="P123">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.6854816021359336E-2</v>
       </c>
       <c r="Q123">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.2078695762059262E-3</v>
       </c>
       <c r="R123">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.1646946445152628E-2</v>
       </c>
     </row>
@@ -9171,51 +9201,51 @@
         <v>178486.955131447</v>
       </c>
       <c r="G124">
-        <f>F124/(E124)</f>
+        <f t="shared" si="29"/>
         <v>1785.2554487557854</v>
       </c>
       <c r="H124">
-        <f>D124/G124</f>
+        <f t="shared" si="30"/>
         <v>43.96855672896087</v>
       </c>
       <c r="I124">
-        <f>C124/G124</f>
+        <f t="shared" si="31"/>
         <v>56.00982746017101</v>
       </c>
-      <c r="J124" s="5">
-        <f>(E124-E123)/E123</f>
+      <c r="J124">
+        <f t="shared" si="32"/>
         <v>2.697670516456909E-3</v>
       </c>
       <c r="K124" s="4">
-        <f>(E124-E120)/E120</f>
+        <f t="shared" si="33"/>
         <v>-6.7284583838754007E-3</v>
       </c>
       <c r="L124">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.8542350672043955</v>
       </c>
       <c r="M124">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.85423506720434306</v>
       </c>
       <c r="N124">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000524</v>
       </c>
       <c r="O124" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2020-3</v>
       </c>
       <c r="P124">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>-1.2476143483607182E-2</v>
       </c>
       <c r="Q124">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.7476850997314286E-3</v>
       </c>
       <c r="R124">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-6.7284583838753687E-3</v>
       </c>
     </row>
@@ -9239,51 +9269,51 @@
         <v>184933.07880181799</v>
       </c>
       <c r="G125">
-        <f>F125/(E125)</f>
+        <f t="shared" si="29"/>
         <v>1847.5745637353866</v>
       </c>
       <c r="H125">
-        <f>D125/G125</f>
+        <f t="shared" si="30"/>
         <v>43.989537699737582</v>
       </c>
       <c r="I125">
-        <f>C125/G125</f>
+        <f t="shared" si="31"/>
         <v>56.105517964984422</v>
       </c>
-      <c r="J125" s="5">
-        <f>(E125-E124)/E124</f>
+      <c r="J125">
+        <f t="shared" si="32"/>
         <v>1.1669670052817098E-3</v>
       </c>
       <c r="K125" s="4">
-        <f>(E125-E121)/E121</f>
+        <f t="shared" si="33"/>
         <v>-1.7187191306018185E-3</v>
       </c>
       <c r="L125">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>-1.5966183837312591</v>
       </c>
       <c r="M125">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>2.5966183837312178</v>
       </c>
       <c r="N125">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.9999999999999587</v>
       </c>
       <c r="O125" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2020-4</v>
       </c>
       <c r="P125">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.7441385603894702E-3</v>
       </c>
       <c r="Q125">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-4.462857690991218E-3</v>
       </c>
       <c r="R125">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>-1.7187191306018423E-3</v>
       </c>
     </row>
@@ -9307,51 +9337,51 @@
         <v>181476.62547701801</v>
       </c>
       <c r="G126">
-        <f>F126/(E126)</f>
+        <f t="shared" si="29"/>
         <v>1798.7688358214371</v>
       </c>
       <c r="H126">
-        <f>D126/G126</f>
+        <f t="shared" si="30"/>
         <v>37.199566420823267</v>
       </c>
       <c r="I126">
-        <f>C126/G126</f>
+        <f t="shared" si="31"/>
         <v>63.689787376627443</v>
       </c>
-      <c r="J126" s="5">
-        <f>(E126-E125)/E125</f>
+      <c r="J126">
+        <f t="shared" si="32"/>
         <v>7.9354382437187999E-3</v>
       </c>
       <c r="K126" s="4">
-        <f>(E126-E122)/E122</f>
+        <f t="shared" si="33"/>
         <v>6.8993273189351728E-3</v>
       </c>
       <c r="L126">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>2.1008282276347727</v>
       </c>
       <c r="M126">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-1.1008282276348551</v>
       </c>
       <c r="N126">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999991762</v>
       </c>
       <c r="O126" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2021-1</v>
       </c>
       <c r="P126">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.4494301583310748E-2</v>
       </c>
       <c r="Q126">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-7.5949742643761434E-3</v>
       </c>
       <c r="R126">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>6.8993273189352777E-3</v>
       </c>
     </row>
@@ -9375,51 +9405,51 @@
         <v>190516.87552611</v>
       </c>
       <c r="G127">
-        <f>F127/(E127)</f>
+        <f t="shared" si="29"/>
         <v>1872.2787261297342</v>
       </c>
       <c r="H127">
-        <f>D127/G127</f>
+        <f t="shared" si="30"/>
         <v>45.759107404935449</v>
       </c>
       <c r="I127">
-        <f>C127/G127</f>
+        <f t="shared" si="31"/>
         <v>55.997577039124138</v>
       </c>
-      <c r="J127" s="5">
-        <f>(E127-E126)/E126</f>
+      <c r="J127">
+        <f t="shared" si="32"/>
         <v>8.5968500536765143E-3</v>
       </c>
       <c r="K127" s="4">
-        <f>(E127-E123)/E123</f>
+        <f t="shared" si="33"/>
         <v>2.0532500890611486E-2</v>
       </c>
       <c r="L127">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.6561770072348423</v>
       </c>
       <c r="M127">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.65617700723504013</v>
       </c>
       <c r="N127">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999980216</v>
       </c>
       <c r="O127" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2021-2</v>
       </c>
       <c r="P127">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>3.4005455876059666E-2</v>
       </c>
       <c r="Q127">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-1.3472954985452241E-2</v>
       </c>
       <c r="R127">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.0532500890611427E-2</v>
       </c>
     </row>
@@ -9443,51 +9473,51 @@
         <v>194587.90720722399</v>
       </c>
       <c r="G128">
-        <f>F128/(E128)</f>
+        <f t="shared" si="29"/>
         <v>1904.6998869641516</v>
       </c>
       <c r="H128">
-        <f>D128/G128</f>
+        <f t="shared" si="30"/>
         <v>46.995744544717425</v>
       </c>
       <c r="I128">
-        <f>C128/G128</f>
+        <f t="shared" si="31"/>
         <v>55.166233066029804</v>
       </c>
-      <c r="J128" s="5">
-        <f>(E128-E127)/E127</f>
+      <c r="J128">
+        <f t="shared" si="32"/>
         <v>3.9829635655022674E-3</v>
       </c>
       <c r="K128" s="4">
-        <f>(E128-E124)/E124</f>
+        <f t="shared" si="33"/>
         <v>2.1840655250882388E-2</v>
       </c>
       <c r="L128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.3863330901214606</v>
       </c>
       <c r="M128">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-0.3863330901213467</v>
       </c>
       <c r="N128">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000001139</v>
       </c>
       <c r="O128" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2021-3</v>
       </c>
       <c r="P128">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>3.0278423084233286E-2</v>
       </c>
       <c r="Q128">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-8.4377678333484099E-3</v>
       </c>
       <c r="R128">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.1840655250882302E-2</v>
       </c>
     </row>
@@ -9511,51 +9541,51 @@
         <v>201697.94426326401</v>
       </c>
       <c r="G129">
-        <f>F129/(E129)</f>
+        <f t="shared" si="29"/>
         <v>1961.2209418057612</v>
       </c>
       <c r="H129">
-        <f>D129/G129</f>
+        <f t="shared" si="30"/>
         <v>46.953572149093006</v>
       </c>
       <c r="I129">
-        <f>C129/G129</f>
+        <f t="shared" si="31"/>
         <v>55.889478301690957</v>
       </c>
-      <c r="J129" s="5">
-        <f>(E129-E128)/E128</f>
+      <c r="J129">
+        <f t="shared" si="32"/>
         <v>6.666598043275916E-3</v>
       </c>
       <c r="K129" s="4">
-        <f>(E129-E125)/E125</f>
+        <f t="shared" si="33"/>
         <v>2.7453851419661338E-2</v>
       </c>
       <c r="L129">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>1.0786172027651513</v>
       </c>
       <c r="M129">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>-7.8617202765169286E-2</v>
       </c>
       <c r="N129">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999998201</v>
       </c>
       <c r="O129" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2021-4</v>
       </c>
       <c r="P129">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.961219642340519E-2</v>
       </c>
       <c r="Q129">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>-2.1583450037443463E-3</v>
       </c>
       <c r="R129">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.745385141966139E-2</v>
       </c>
     </row>
@@ -9579,51 +9609,51 @@
         <v>199637.42051132201</v>
       </c>
       <c r="G130">
-        <f>F130/(E130)</f>
+        <f t="shared" ref="G130:G161" si="34">F130/(E130)</f>
         <v>1912.4177640689477</v>
       </c>
       <c r="H130">
-        <f>D130/G130</f>
+        <f t="shared" ref="H130:H161" si="35">D130/G130</f>
         <v>38.746551067544516</v>
       </c>
       <c r="I130">
-        <f>C130/G130</f>
+        <f t="shared" ref="I130:I146" si="36">C130/G130</f>
         <v>65.643516972068369</v>
       </c>
-      <c r="J130" s="5">
-        <f>(E130-E129)/E129</f>
+      <c r="J130">
+        <f t="shared" si="32"/>
         <v>1.5042509747115339E-2</v>
       </c>
       <c r="K130" s="4">
-        <f>(E130-E126)/E126</f>
+        <f t="shared" si="33"/>
         <v>3.4698549553505528E-2</v>
       </c>
       <c r="L130">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.44190543406532024</v>
       </c>
       <c r="M130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.5580945659347285</v>
       </c>
       <c r="N130">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000488</v>
       </c>
       <c r="O130" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2022-1</v>
       </c>
       <c r="P130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.5333477601878883E-2</v>
       </c>
       <c r="Q130">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.9365071951628336E-2</v>
       </c>
       <c r="R130">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>3.4698549553505487E-2</v>
       </c>
     </row>
@@ -9647,51 +9677,51 @@
         <v>204207.29051331399</v>
       </c>
       <c r="G131">
-        <f>F131/(E131)</f>
+        <f t="shared" si="34"/>
         <v>1947.2676704075552</v>
       </c>
       <c r="H131">
-        <f>D131/G131</f>
+        <f t="shared" si="35"/>
         <v>47.60277680669877</v>
       </c>
       <c r="I131">
-        <f>C131/G131</f>
+        <f t="shared" si="36"/>
         <v>57.265851999003303</v>
       </c>
-      <c r="J131" s="5">
-        <f>(E131-E130)/E130</f>
+      <c r="J131">
+        <f t="shared" ref="J131:J146" si="37">(E131-E130)/E130</f>
         <v>4.5843515104080947E-3</v>
       </c>
       <c r="K131" s="4">
-        <f>(E131-E127)/E127</f>
+        <f t="shared" si="33"/>
         <v>3.0582210678776308E-2</v>
       </c>
       <c r="L131">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.59244934597433418</v>
       </c>
       <c r="M131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.40755065402582108</v>
       </c>
       <c r="N131">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000001552</v>
       </c>
       <c r="O131" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2022-2</v>
       </c>
       <c r="P131">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.8118410715090322E-2</v>
       </c>
       <c r="Q131">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.2463799963690734E-2</v>
       </c>
       <c r="R131">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>3.0582210678776311E-2</v>
       </c>
     </row>
@@ -9715,51 +9745,51 @@
         <v>205117.94364216799</v>
       </c>
       <c r="G132">
-        <f>F132/(E132)</f>
+        <f t="shared" si="34"/>
         <v>1948.5553374121523</v>
       </c>
       <c r="H132">
-        <f>D132/G132</f>
+        <f t="shared" si="35"/>
         <v>49.574973765651471</v>
       </c>
       <c r="I132">
-        <f>C132/G132</f>
+        <f t="shared" si="36"/>
         <v>55.691702373288322</v>
       </c>
-      <c r="J132" s="5">
-        <f>(E132-E131)/E131</f>
+      <c r="J132">
+        <f t="shared" si="37"/>
         <v>3.7956759592565042E-3</v>
       </c>
       <c r="K132" s="4">
-        <f>(E132-E128)/E128</f>
+        <f t="shared" si="33"/>
         <v>3.0389961126461168E-2</v>
       </c>
       <c r="L132">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.8307502958862848</v>
       </c>
       <c r="M132">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.16924970411357554</v>
       </c>
       <c r="N132">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>0.99999999999986033</v>
       </c>
       <c r="O132" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2022-3</v>
       </c>
       <c r="P132">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>2.5246469197780307E-2</v>
       </c>
       <c r="Q132">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>5.1434919286766157E-3</v>
       </c>
       <c r="R132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>3.0389961126461085E-2</v>
       </c>
     </row>
@@ -9783,51 +9813,51 @@
         <v>210741.03205271999</v>
       </c>
       <c r="G133">
-        <f>F133/(E133)</f>
+        <f t="shared" si="34"/>
         <v>1995.1069123441882</v>
       </c>
       <c r="H133">
-        <f>D133/G133</f>
+        <f t="shared" si="35"/>
         <v>48.428435113852515</v>
       </c>
       <c r="I133">
-        <f>C133/G133</f>
+        <f t="shared" si="36"/>
         <v>57.200506748268566</v>
       </c>
-      <c r="J133" s="5">
-        <f>(E133-E132)/E132</f>
+      <c r="J133">
+        <f t="shared" si="37"/>
         <v>3.4414093468938573E-3</v>
       </c>
       <c r="K133" s="4">
-        <f>(E133-E129)/E129</f>
+        <f t="shared" si="33"/>
         <v>2.7088766806564059E-2</v>
       </c>
       <c r="L133">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.52940432593950271</v>
       </c>
       <c r="M133">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.47059567406054315</v>
       </c>
       <c r="N133">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000457</v>
       </c>
       <c r="O133" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2022-4</v>
       </c>
       <c r="P133">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>1.4340910331761421E-2</v>
       </c>
       <c r="Q133">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.274785647480388E-2</v>
       </c>
       <c r="R133">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.7088766806564024E-2</v>
       </c>
     </row>
@@ -9851,51 +9881,51 @@
         <v>207392.577930439</v>
       </c>
       <c r="G134">
-        <f>F134/(E134)</f>
+        <f t="shared" si="34"/>
         <v>1947.0164307215857</v>
       </c>
       <c r="H134">
-        <f>D134/G134</f>
+        <f t="shared" si="35"/>
         <v>39.551953420284619</v>
       </c>
       <c r="I134">
-        <f>C134/G134</f>
+        <f t="shared" si="36"/>
         <v>66.966191294897371</v>
       </c>
-      <c r="J134" s="5">
-        <f>(E134-E133)/E133</f>
+      <c r="J134">
+        <f t="shared" si="37"/>
         <v>8.4181743884332114E-3</v>
       </c>
       <c r="K134" s="4">
-        <f>(E134-E130)/E130</f>
+        <f t="shared" ref="K134:K165" si="38">(E134-E130)/E130</f>
         <v>2.0385815581243437E-2</v>
       </c>
       <c r="L134">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>0.37846491246597319</v>
       </c>
       <c r="M134">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>0.62153508753407349</v>
       </c>
       <c r="N134">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000466</v>
       </c>
       <c r="O134" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="25"/>
         <v>Q2023-1</v>
       </c>
       <c r="P134">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>7.7153159095027695E-3</v>
       </c>
       <c r="Q134">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>1.2670499671741619E-2</v>
       </c>
       <c r="R134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="28"/>
         <v>2.0385815581243527E-2</v>
       </c>
     </row>
@@ -9919,51 +9949,51 @@
         <v>207764.86587616199</v>
       </c>
       <c r="G135">
-        <f>F135/(E135)</f>
+        <f t="shared" si="34"/>
         <v>1958.2689276951212</v>
       </c>
       <c r="H135">
-        <f>D135/G135</f>
+        <f t="shared" si="35"/>
         <v>47.005476868268701</v>
       </c>
       <c r="I135">
-        <f>C135/G135</f>
+        <f t="shared" si="36"/>
         <v>59.09070989025799</v>
       </c>
-      <c r="J135" s="5">
-        <f>(E135-E134)/E134</f>
+      <c r="J135">
+        <f t="shared" si="37"/>
         <v>-3.9613716309392791E-3</v>
       </c>
       <c r="K135" s="4">
-        <f>(E135-E131)/E131</f>
+        <f t="shared" si="38"/>
         <v>1.1705673725355787E-2</v>
       </c>
       <c r="L135">
-        <f t="shared" ref="L135:L146" si="14">(H135-H131)/(E135-E131)</f>
+        <f t="shared" ref="L135:L146" si="39">(H135-H131)/(E135-E131)</f>
         <v>-0.48657575559304161</v>
       </c>
       <c r="M135">
-        <f t="shared" ref="M135:M146" si="15">(I135-I131)/(E135-E131)</f>
+        <f t="shared" ref="M135:M146" si="40">(I135-I131)/(E135-E131)</f>
         <v>1.4865757555927348</v>
       </c>
       <c r="N135">
-        <f t="shared" ref="N135:N146" si="16">M135+L135</f>
+        <f t="shared" ref="N135:N146" si="41">M135+L135</f>
         <v>0.99999999999969313</v>
       </c>
       <c r="O135" t="str">
-        <f t="shared" ref="O135:O146" si="17">"Q"&amp;A135&amp;"-"&amp;B135</f>
+        <f t="shared" ref="O135:O146" si="42">"Q"&amp;A135&amp;"-"&amp;B135</f>
         <v>Q2023-2</v>
       </c>
       <c r="P135">
-        <f t="shared" ref="P135:P146" si="18">L135*K135</f>
+        <f t="shared" ref="P135:P146" si="43">L135*K135</f>
         <v>-5.6956970376406063E-3</v>
       </c>
       <c r="Q135">
-        <f t="shared" ref="Q135:Q146" si="19">M135*K135</f>
+        <f t="shared" ref="Q135:Q146" si="44">M135*K135</f>
         <v>1.7401370762992804E-2</v>
       </c>
       <c r="R135">
-        <f t="shared" ref="R135:R146" si="20">E135/E131-1</f>
+        <f t="shared" ref="R135:R146" si="45">E135/E131-1</f>
         <v>1.1705673725355803E-2</v>
       </c>
     </row>
@@ -9987,51 +10017,51 @@
         <v>207293.36781984899</v>
       </c>
       <c r="G136">
-        <f>F136/(E136)</f>
+        <f t="shared" si="34"/>
         <v>1954.8590534693546</v>
       </c>
       <c r="H136">
-        <f>D136/G136</f>
+        <f t="shared" si="35"/>
         <v>48.302425938480688</v>
       </c>
       <c r="I136">
-        <f>C136/G136</f>
+        <f t="shared" si="36"/>
         <v>57.737632270298299</v>
       </c>
-      <c r="J136" s="5">
-        <f>(E136-E135)/E135</f>
+      <c r="J136">
+        <f t="shared" si="37"/>
         <v>-5.2903456253091655E-4</v>
       </c>
       <c r="K136" s="4">
-        <f>(E136-E132)/E132</f>
+        <f t="shared" si="38"/>
         <v>7.346884106212548E-3</v>
       </c>
       <c r="L136">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>-1.6454322860571287</v>
       </c>
       <c r="M136">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>2.6454322860573769</v>
       </c>
       <c r="N136">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000002482</v>
       </c>
       <c r="O136" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2023-3</v>
       </c>
       <c r="P136">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-1.2088800310282097E-2</v>
       </c>
       <c r="Q136">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>1.9435684416496467E-2</v>
       </c>
       <c r="R136">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>7.3468841062125367E-3</v>
       </c>
     </row>
@@ -10055,51 +10085,51 @@
         <v>211738.99966246501</v>
       </c>
       <c r="G137">
-        <f>F137/(E137)</f>
+        <f t="shared" si="34"/>
         <v>2007.6246575982047</v>
       </c>
       <c r="H137">
-        <f>D137/G137</f>
+        <f t="shared" si="35"/>
         <v>46.876280988312935</v>
       </c>
       <c r="I137">
-        <f>C137/G137</f>
+        <f t="shared" si="36"/>
         <v>58.591142347569054</v>
       </c>
-      <c r="J137" s="5">
-        <f>(E137-E136)/E136</f>
+      <c r="J137">
+        <f t="shared" si="37"/>
         <v>-5.4001750147058105E-3</v>
       </c>
       <c r="K137" s="4">
-        <f>(E137-E133)/E133</f>
+        <f t="shared" si="38"/>
         <v>-1.529112413620742E-3</v>
       </c>
       <c r="L137">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>9.6097590888299482</v>
       </c>
       <c r="M137">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>-8.6097590888293318</v>
       </c>
       <c r="N137">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000006164</v>
       </c>
       <c r="O137" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2023-4</v>
       </c>
       <c r="P137">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-1.4694401914634624E-2</v>
       </c>
       <c r="Q137">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>1.316528950101294E-2</v>
       </c>
       <c r="R137">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>-1.5291124136207479E-3</v>
       </c>
     </row>
@@ -10123,51 +10153,51 @@
         <v>208817.70960822399</v>
       </c>
       <c r="G138">
-        <f>F138/(E138)</f>
+        <f t="shared" si="34"/>
         <v>1950.6863945977527</v>
       </c>
       <c r="H138">
-        <f>D138/G138</f>
+        <f t="shared" si="35"/>
         <v>37.959338070317557</v>
       </c>
       <c r="I138">
-        <f>C138/G138</f>
+        <f t="shared" si="36"/>
         <v>69.088986143418438</v>
       </c>
-      <c r="J138" s="5">
-        <f>(E138-E137)/E137</f>
+      <c r="J138">
+        <f t="shared" si="37"/>
         <v>1.4989470946107201E-2</v>
       </c>
       <c r="K138" s="4">
-        <f>(E138-E134)/E134</f>
+        <f t="shared" si="38"/>
         <v>4.9773632461552345E-3</v>
       </c>
       <c r="L138">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>-3.0039172663423468</v>
       </c>
       <c r="M138">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>4.0039172663423734</v>
       </c>
       <c r="N138">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000000266</v>
       </c>
       <c r="O138" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2024-1</v>
       </c>
       <c r="P138">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-1.4951587395983502E-2</v>
       </c>
       <c r="Q138">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>1.9928950642138867E-2</v>
       </c>
       <c r="R138">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>4.9773632461551642E-3</v>
       </c>
     </row>
@@ -10191,51 +10221,51 @@
         <v>213160.36547572399</v>
       </c>
       <c r="G139">
-        <f>F139/(E139)</f>
+        <f t="shared" si="34"/>
         <v>1995.0541207578256</v>
       </c>
       <c r="H139">
-        <f>D139/G139</f>
+        <f t="shared" si="35"/>
         <v>46.559358397658819</v>
       </c>
       <c r="I139">
-        <f>C139/G139</f>
+        <f t="shared" si="36"/>
         <v>60.285044096422538</v>
       </c>
-      <c r="J139" s="5">
-        <f>(E139-E138)/E138</f>
+      <c r="J139">
+        <f t="shared" si="37"/>
         <v>-1.9049501349301221E-3</v>
       </c>
       <c r="K139" s="4">
-        <f>(E139-E135)/E135</f>
+        <f t="shared" si="38"/>
         <v>7.0522396554828469E-3</v>
       </c>
       <c r="L139">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>-0.59624310130227931</v>
       </c>
       <c r="M139">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>1.5962431013031719</v>
       </c>
       <c r="N139">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000008926</v>
       </c>
       <c r="O139" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2024-2</v>
       </c>
       <c r="P139">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-4.2048492433120104E-3</v>
       </c>
       <c r="Q139">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>1.1257088898801152E-2</v>
       </c>
       <c r="R139">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>7.0522396554828504E-3</v>
       </c>
     </row>
@@ -10259,51 +10289,51 @@
         <v>214032.611491252</v>
       </c>
       <c r="G140">
-        <f>F140/(E140)</f>
+        <f t="shared" si="34"/>
         <v>1993.8903016882148</v>
       </c>
       <c r="H140">
-        <f>D140/G140</f>
+        <f t="shared" si="35"/>
         <v>49.023968085604075</v>
       </c>
       <c r="I140">
-        <f>C140/G140</f>
+        <f t="shared" si="36"/>
         <v>58.320258078710189</v>
       </c>
-      <c r="J140" s="5">
-        <f>(E140-E139)/E139</f>
+      <c r="J140">
+        <f t="shared" si="37"/>
         <v>4.6780519949155821E-3</v>
       </c>
       <c r="K140" s="4">
-        <f>(E140-E136)/E136</f>
+        <f t="shared" si="38"/>
         <v>1.2298823459406793E-2</v>
       </c>
       <c r="L140">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>0.55325860757512424</v>
       </c>
       <c r="M140">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>0.44674139242509375</v>
       </c>
       <c r="N140">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.000000000000218</v>
       </c>
       <c r="O140" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2024-3</v>
       </c>
       <c r="P140">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>6.8044299419636745E-3</v>
       </c>
       <c r="Q140">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>5.4943935174457991E-3</v>
       </c>
       <c r="R140">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>1.2298823459406805E-2</v>
       </c>
     </row>
@@ -10327,51 +10357,51 @@
         <v>217946.298203721</v>
       </c>
       <c r="G141">
-        <f>F141/(E141)</f>
+        <f t="shared" si="34"/>
         <v>2037.5264934668676</v>
       </c>
       <c r="H141">
-        <f>D141/G141</f>
+        <f t="shared" si="35"/>
         <v>47.438856683168694</v>
       </c>
       <c r="I141">
-        <f>C141/G141</f>
+        <f t="shared" si="36"/>
         <v>59.527260764896297</v>
       </c>
-      <c r="J141" s="5">
-        <f>(E141-E140)/E140</f>
+      <c r="J141">
+        <f t="shared" si="37"/>
         <v>-3.5223945409994339E-3</v>
       </c>
       <c r="K141" s="4">
-        <f>(E141-E137)/E137</f>
+        <f t="shared" si="38"/>
         <v>1.4210019215223578E-2</v>
       </c>
       <c r="L141">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>0.37537726363407792</v>
       </c>
       <c r="M141">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>0.62462273636592203</v>
       </c>
       <c r="N141">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="O141" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2024-4</v>
       </c>
       <c r="P141">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>5.3341181291982941E-3</v>
       </c>
       <c r="Q141">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>8.8759010860252827E-3</v>
       </c>
       <c r="R141">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>1.4210019215223468E-2</v>
       </c>
     </row>
@@ -10395,51 +10425,51 @@
         <v>216122.687114189</v>
       </c>
       <c r="G142">
-        <f>F142/(E142)</f>
+        <f t="shared" si="34"/>
         <v>2001.1724826740835</v>
       </c>
       <c r="H142">
-        <f>D142/G142</f>
+        <f t="shared" si="35"/>
         <v>39.847999864332387</v>
       </c>
       <c r="I142">
-        <f>C142/G142</f>
+        <f t="shared" si="36"/>
         <v>68.150030782877906</v>
       </c>
-      <c r="J142" s="5">
-        <f>(E142-E141)/E141</f>
+      <c r="J142">
+        <f t="shared" si="37"/>
         <v>9.6471034357773836E-3</v>
       </c>
       <c r="K142" s="4">
-        <f>(E142-E138)/E138</f>
+        <f t="shared" si="38"/>
         <v>8.8717543263712624E-3</v>
       </c>
       <c r="L142">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>1.9886795829171602</v>
       </c>
       <c r="M142">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>-0.98867958291685332</v>
       </c>
       <c r="N142">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000003069</v>
       </c>
       <c r="O142" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2025-1</v>
       </c>
       <c r="P142">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>1.7643076693511513E-2</v>
       </c>
       <c r="Q142">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>-8.7713223671375285E-3</v>
       </c>
       <c r="R142">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>8.8717543263712173E-3</v>
       </c>
     </row>
@@ -10463,51 +10493,51 @@
         <v>217608.29839459399</v>
       </c>
       <c r="G143">
-        <f>F143/(E143)</f>
+        <f t="shared" si="34"/>
         <v>2022.9421570212119</v>
       </c>
       <c r="H143">
-        <f>D143/G143</f>
+        <f t="shared" si="35"/>
         <v>47.662482280502687</v>
       </c>
       <c r="I143">
-        <f>C143/G143</f>
+        <f t="shared" si="36"/>
         <v>59.907720673309022</v>
       </c>
-      <c r="J143" s="5">
-        <f>(E143-E142)/E142</f>
+      <c r="J143">
+        <f t="shared" si="37"/>
         <v>-3.9614397673190666E-3</v>
       </c>
       <c r="K143" s="4">
-        <f>(E143-E139)/E139</f>
+        <f t="shared" si="38"/>
         <v>6.793060214560262E-3</v>
       </c>
       <c r="L143">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>1.5198721191947242</v>
       </c>
       <c r="M143">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>-0.51987211919562493</v>
       </c>
       <c r="N143">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>0.99999999999909928</v>
       </c>
       <c r="O143" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2025-2</v>
       </c>
       <c r="P143">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>1.0324582824121074E-2</v>
       </c>
       <c r="Q143">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>-3.53152260956693E-3</v>
       </c>
       <c r="R143">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>6.7930602145602759E-3</v>
       </c>
     </row>
@@ -10531,51 +10561,51 @@
         <v>215393.70572398399</v>
       </c>
       <c r="G144">
-        <f>F144/(E144)</f>
+        <f t="shared" si="34"/>
         <v>2007.1435708097079</v>
       </c>
       <c r="H144">
-        <f>D144/G144</f>
+        <f t="shared" si="35"/>
         <v>47.705836045506871</v>
       </c>
       <c r="I144">
-        <f>C144/G144</f>
+        <f t="shared" si="36"/>
         <v>59.607715838124207</v>
       </c>
-      <c r="J144" s="5">
-        <f>(E144-E143)/E143</f>
+      <c r="J144">
+        <f t="shared" si="37"/>
         <v>-2.3858937060032589E-3</v>
       </c>
       <c r="K144" s="4">
-        <f>(E144-E140)/E140</f>
+        <f t="shared" si="38"/>
         <v>-2.8575622349760705E-4</v>
       </c>
       <c r="L144">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>42.971897327270277</v>
       </c>
       <c r="M144">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>-41.971897327263797</v>
       </c>
       <c r="N144">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000064801</v>
       </c>
       <c r="O144" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2025-3</v>
       </c>
       <c r="P144">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-1.2279487096767669E-2</v>
       </c>
       <c r="Q144">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>1.1993730873268209E-2</v>
       </c>
       <c r="R144">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>-2.8575622349757968E-4</v>
       </c>
     </row>
@@ -10599,51 +10629,51 @@
         <v>218669.78646519</v>
       </c>
       <c r="G145">
-        <f>F145/(E145)</f>
+        <f t="shared" si="34"/>
         <v>2057.673982562233</v>
       </c>
       <c r="H145">
-        <f>D145/G145</f>
+        <f t="shared" si="35"/>
         <v>46.776978627179595</v>
       </c>
       <c r="I145">
-        <f>C145/G145</f>
+        <f t="shared" si="36"/>
         <v>59.493396718141447</v>
       </c>
-      <c r="J145" s="5">
-        <f>(E145-E144)/E144</f>
+      <c r="J145">
+        <f t="shared" si="37"/>
         <v>-9.7208276121659824E-3</v>
       </c>
       <c r="K145" s="4">
-        <f>(E145-E141)/E141</f>
+        <f t="shared" si="38"/>
         <v>-6.5043222970283861E-3</v>
       </c>
       <c r="L145">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>0.95132672491524206</v>
       </c>
       <c r="M145">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>4.8673275084676254E-2</v>
       </c>
       <c r="N145">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>0.99999999999991829</v>
       </c>
       <c r="O145" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2025-4</v>
       </c>
       <c r="P145">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-6.1877356286251985E-3</v>
       </c>
       <c r="Q145">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>-3.1658666840265597E-4</v>
       </c>
       <c r="R145">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>-6.5043222970283532E-3</v>
       </c>
     </row>
@@ -10667,51 +10697,51 @@
         <v>216625.62274590699</v>
       </c>
       <c r="G146">
-        <f>F146/(E146)</f>
+        <f t="shared" si="34"/>
         <v>2010.7030535786139</v>
       </c>
       <c r="H146">
-        <f>D146/G146</f>
+        <f t="shared" si="35"/>
         <v>39.355062691582475</v>
       </c>
       <c r="I146">
-        <f>C146/G146</f>
+        <f t="shared" si="36"/>
         <v>68.381195211025371</v>
       </c>
-      <c r="J146" s="5">
-        <f>(E146-E145)/E145</f>
+      <c r="J146">
+        <f t="shared" si="37"/>
         <v>1.3793896488308061E-2</v>
       </c>
       <c r="K146" s="4">
-        <f>(E146-E142)/E142</f>
+        <f t="shared" si="38"/>
         <v>-2.4238659078619131E-3</v>
       </c>
       <c r="L146">
-        <f t="shared" si="14"/>
+        <f t="shared" si="39"/>
         <v>1.8830729436686684</v>
       </c>
       <c r="M146">
-        <f t="shared" si="15"/>
+        <f t="shared" si="40"/>
         <v>-0.88307294366695843</v>
       </c>
       <c r="N146">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>1.00000000000171</v>
       </c>
       <c r="O146" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>Q2026-1</v>
       </c>
       <c r="P146">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>-4.5643163101756618E-3</v>
       </c>
       <c r="Q146">
-        <f t="shared" si="19"/>
+        <f t="shared" si="44"/>
         <v>2.1404504023096044E-3</v>
       </c>
       <c r="R146">
-        <f t="shared" si="20"/>
+        <f t="shared" si="45"/>
         <v>-2.4238659078619218E-3</v>
       </c>
     </row>

--- a/posts/inflation suisse/inflation_income_decomposition.xlsx
+++ b/posts/inflation suisse/inflation_income_decomposition.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8C5CA1-E420-42CA-8B4A-4C596758C130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E69DC64F-2C82-4DC4-BC99-01B9323A830B}"/>
   </bookViews>
   <sheets>
     <sheet name="data source" sheetId="3" r:id="rId1"/>
@@ -1261,7 +1261,7 @@
         <v>1.2116298570874309E-2</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" ref="K6:K37" si="4">(E7-E3)/E3</f>
+        <f t="shared" ref="K7:K37" si="4">(E7-E3)/E3</f>
         <v>5.6838058528058788E-2</v>
       </c>
       <c r="L7">
@@ -9609,11 +9609,11 @@
         <v>199637.42051132201</v>
       </c>
       <c r="G130">
-        <f t="shared" ref="G130:G161" si="34">F130/(E130)</f>
+        <f t="shared" ref="G130:G146" si="34">F130/(E130)</f>
         <v>1912.4177640689477</v>
       </c>
       <c r="H130">
-        <f t="shared" ref="H130:H161" si="35">D130/G130</f>
+        <f t="shared" ref="H130:H146" si="35">D130/G130</f>
         <v>38.746551067544516</v>
       </c>
       <c r="I130">
@@ -9897,7 +9897,7 @@
         <v>8.4181743884332114E-3</v>
       </c>
       <c r="K134" s="4">
-        <f t="shared" ref="K134:K165" si="38">(E134-E130)/E130</f>
+        <f t="shared" ref="K134:K146" si="38">(E134-E130)/E130</f>
         <v>2.0385815581243437E-2</v>
       </c>
       <c r="L134">
